--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. 요구사항 상태" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Launch 차단 - 사용자 필요" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Launch 하드닝 이력" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 보안 감사" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3717,4 +3718,266 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>영역</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>점검 항목</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>근거/조치</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>응답 헤더</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>HSTS·X-Content-Type-Options·X-Frame-Options·Referrer-Policy·Permissions-Policy</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>조치완료(9.8)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>전무했음 → nginx snippet 추가·server_tokens off·E2E 무결·회귀게이트 12/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>응답 헤더</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Content-Security-Policy</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>조치완료(9.9)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>frame-ancestors/base-uri/object-src 최소 CSP(Next 무영향). script-src 전체 CSP 는 후속</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>CORS</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>교차 출처 허용 범위</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>localhost 전용 잠김·evil origin 미반사. 앱은 Next SSR 서버측 호출이라 CORS 무관</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>세션 쿠키</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>httpOnly·SameSite·Secure</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>httpOnly+sameSite:lax+secure(NODE_ENV=production 확인)·8h 만료</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>시크릿</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>커밋된 자격증명/키</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>추적 파일 하드코딩 시크릿 0·.env/.pem/.key/oauth 미추적</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SQL 인젝션</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>동적 쿼리 식별자·ORDER BY 보간</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ORDER BY 전량 화이트리스트(DOC/PRICE/HISTORY_SORT)·식별자 전량 코드상수/allowlist·파라미터 직접보간 0건(AST 전수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>로그인 무차별 대입</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>속도제한(429)·5회 실패 자동잠금·MFA(TOTP)·보안 이상 관측(9.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>테넌트 격리</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>교차 테넌트 데이터 접근</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>정적 게이트(tenant-scope 68항목)+라이브(tenant_isolation·ai_prep 교차차단)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>인가</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>승인·배포 동사·정보 마스킹</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>verb-guard 게이트·masking 전경로(8.3/8.4)·승인결과 직접쓰기 차단(8.7~8.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>배포</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>마이그레이션 실패·헬스</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>autodeploy health-gate+자동롤백. 이번 세션 마이그레이션 전량 additive(하위호환)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Launch 차단 - 사용자 필요" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Launch 하드닝 이력" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 보안 감사" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 품질·설계 결정" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3530,7 +3531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3712,6 +3713,138 @@
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>라이브 8/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Launch 준비 딜리버러블</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>요구/차단/하드닝 xlsx</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>보안 응답 헤더</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>HSTS·nosniff·X-Frame·Referrer·버전숨김</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>최소 CSP + 보안 감사</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>frame-ancestors·base-uri·object-src·CORS/쿠키/시크릿</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>E2E 무결</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>9.10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>보안 감사 시트</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SQL인젝션 전수(AST 0건) 등 10영역</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>플릿 동시실행 락</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>시드 손상 유발 충돌 방지</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>뮤테이션 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>9.12</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>a11y: html lang</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>ko 하드코딩→실 로케일(en/ja/zh)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>라이브 확인</t>
         </is>
       </c>
     </row>
@@ -3980,4 +4113,108 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>html lang 로케일</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(9.12)</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>en/ja/zh 사용자에게 실 로케일 선언 — 라이브 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>색상 대비(muted 텍스트)</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>설계 결정 필요</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>주 텍스트 15:1(우수). --txt-mute #8B93A1 ≈3.2:1 은 WCAG AA 일반텍스트(4.5:1) 미달·큰텍스트(3:1) 통과. 의도적 약화 텍스트라 darken 은 시각 위계 변경 — 디자인 소유자 판단</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Head Type 목록(#77)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>결정 필요</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Freeze 6종 vs 코드 SYSTEM/TENANT 2종 — 권한 임계 필드</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>전체 CSP script-src</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>후속</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>현재 최소 CSP. script-src 는 Next 인라인 검증 후</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -617,31 +617,31 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>전 화면 E2E 브라우저 스윕 (62화면·쓰기·결재·명령줄)</t>
+          <t>전 화면 로그인 SSR 렌더 스윕 (60화면·인증 200 무오류)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS 60/60</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>핵심 매출 파이프라인 (CPQ→BOM→치수→도면→단가→견적PDF)</t>
+          <t>라이브 API 플릿 (105 스위트·실 HTTP+psql 검증)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS 105/105</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>정적 게이트 6종 (테넌트/커서/동사/거버넌스/FK/잔재)</t>
+          <t>정적 게이트 7종 (테넌트/커서/동사/거버넌스/FK/잔재/i18n)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>P0/P1 요구사항 63/63 구현·검증 완료. 구현 스코프에서 launch 가능. 잔여는 사용자 결정·AI 크레딧 대기.</t>
+          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝 전면(9.16~9.22) + 마스터 대장 검색(9.23~9.25). 전 화면 60/60·플릿 105/105 실측. 구현 스코프에서 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기.</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3845,6 +3845,270 @@
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>라이브 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>9.14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>AI 질의 감사 추적</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>#64 ai_chat 감사(질문·참조·사용자)·alembic 0054 SECURITY 소스</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>라이브 6/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>9.15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Macro AI 무상태 불변식</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>#65 macro-generate 초안만 반환·게시 불가</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>라이브 7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9.16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>DB 풀 상향</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>min1/max4→min2/max12 (읽기 동시성 병목 해소)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>부하 재측정</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>9.17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>실시간 DB 부하 신호</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>/system/status dbLoad(활성쿼리·최장쿼리)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>라이브 9/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>9.18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>프로젝트 채번 경쟁 수정</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>동시 생성 500(12중7)→ON CONFLICT 재시도 전량 201</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>라이브 5/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>9.19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>채번기 5종 경쟁 안전화</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>eco/wo/qc/po/산출물 동일 버그 클래스 전수 제거</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>라이브 5/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>9.20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>트랜잭션 그리드 안전 상한</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>무한성장 7종 최신순 limit 회로차단(OOM 방지)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>라이브 18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>9.21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>내보내기 메모리 상한</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>export.xlsx 6종 LIMIT+절단 고지(공유 백엔드 OOM)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>라이브 20/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9.22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>잔여 그리드 상한</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>anomalies·supplier-evals 상한 + 전 플릿 105/105</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>라이브 24/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>9.23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>마스터 검색: 부품·거래처</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>서버측 q 부분일치(ILIKE, 하위호환)·SearchBox</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>라이브 10/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>마스터 검색: 자재·도면</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>동일 패턴 확장</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>라이브 17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>9.25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>마스터 검색: 제품코드</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>대형 마스터 5종 전부 검색 가능</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>라이브 21/21</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -4435,12 +4435,12 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>설계 결정 필요</t>
+          <t>조치완료(9.38)</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>주 텍스트 15:1(우수). --txt-mute #8B93A1 ≈3.2:1 은 WCAG AA 일반텍스트(4.5:1) 미달·큰텍스트(3:1) 통과. 의도적 약화 텍스트라 darken 은 시각 위계 변경 — 디자인 소유자 판단</t>
+          <t>--txt-mute #8B93A1(3.09:1, AA 미달)→#626A7A 로 어둡게 — 흰색 5.44·회색패널 4.5+ 로 WCAG AA 충족, 텍스트 계층 유지</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -617,31 +617,31 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>전 화면 로그인 SSR 렌더 스윕 (60화면·인증 200 무오류)</t>
+          <t>전 화면 로그인 SSR 렌더 스윕 (62화면·인증 200 무오류)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PASS 60/60</t>
+          <t>PASS 62/62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (105 스위트·실 HTTP+psql 검증)</t>
+          <t>라이브 API 플릿 (108 스위트·실 HTTP+psql, 시드 자기치유)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 105/105</t>
+          <t>PASS 108/108</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>정적 게이트 7종 (테넌트/커서/동사/거버넌스/FK/잔재/i18n)</t>
+          <t>정적/브라우저 게이트 9종 (테넌트/커서/동사/거버넌스/FK/잔재/i18n 62화면/a11y 이름 62화면)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝 전면(9.16~9.22) + 마스터 대장 검색(9.23~9.25). 전 화면 60/60·플릿 105/105 실측. 구현 스코프에서 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기.</t>
+          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝 전면(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31) ·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(대비/포커스/이름/키보드, 9.38~9.41). 전 화면 62/62·플릿 108/108 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기.</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4109,6 +4109,402 @@
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>라이브 21/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>9.26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Launch 딜리버러블 갱신</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>하드닝 9.14~9.25·검증상태 반영</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>9.27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>상한 도달 정직 표기</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>트랜잭션 그리드 상한 칩(무음 상한 제거)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>UI 7그리드</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>9.28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>검색 0건 상태 정정</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>'검색 결과 없음' vs '대장 비어있음' 구분</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>searchActive 5그리드</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>9.29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>검색 LIKE 메타문자 이스케이프</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>q 검색 %·_ 와일드카드 오매칭 제거</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>live 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>9.29a</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>LIKE 이스케이프 클래스 전수</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>전역검색·AI·감사필터·중복검사·승인이력</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>미이스케이프 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>9.30</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>트랜잭션 그리드 검색</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>작업지시·검사·설계변경 q 부분일치</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>라이브 35/35</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>9.31</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>발주·원가실적 검색 + 상한 수정</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>/erp/pos 무한성장 누락 상한 신설</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>라이브 41/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>9.31a</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>성장테이블 전수 재감사</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>문서함(/documents) 검색·상한 보완</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>23개소 감사</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>9.32</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>오형식 날짜 500→422</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>_valid_date 6개소 + 계층주소 LIKE 이스케이프</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>live 7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>검색 UI i18n 파리티</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>플릿이 발굴 — SearchBox 한글폴백 번역</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>게이트 통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>9.34</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>i18n 게이트 커버리지 +6화면</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>검사·원가·제품코드 영문화(25건)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>39화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>i18n 게이트 62화면 완전 커버</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>잔여 43건 영문화(공용메뉴·ECO대장 등)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>62/62</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>시드 무결성 자기치유</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>seed_heal — 중단 플릿의 BOM 훼손 멱등 복원</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>delete→heal→PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>정보접근 마스킹 우회 차단</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>발주·재고·구매요청 cost/partner 마스킹(누출 클래스)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>라이브 41/41</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>9.38</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>a11y: 색상 대비 WCAG AA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>muted 텍스트 3.09:1→4.5+:1</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>전 배경 4.5+</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>9.39</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>a11y: 키보드 포커스 가시성</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>버튼·링크·탭 :focus-visible(WCAG 2.4.7)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CSS 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>9.40</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>a11y: 접근가능 이름 게이트</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 62화면 + 아이콘버튼 4건(WCAG 4.1.2)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>62/62</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>9.41</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>a11y: 키보드 조작 헬퍼</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>kbdClick + Head 토글(WCAG 2.1.1), 그리드는 기존 완전지원</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>tsc·DOM 검증</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4478,6 +4874,57 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>a11y: 키보드 포커스</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(9.39)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>버튼·링크·탭 :focus-visible 아웃라인 — WCAG 2.4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>a11y: 접근가능 이름</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(9.40)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Playwright 게이트 62화면 + 아이콘버튼 4건 aria-label/title — WCAG 4.1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>a11y: 키보드 조작</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>진행(9.41)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>kbdClick 헬퍼·핵심 그리드 완전지원·Head 토글 적용. 커스텀 컨트롤 후속 롤아웃 — WCAG 2.1.1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -675,16 +675,28 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>성능 확장성 — 핵심 쿼리 인덱스 백업 (재귀 BOM·감사로그·원가·발주집계·where-used)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED (index-backed)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝 전면(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31) ·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(대비/포커스/이름/키보드, 9.38~9.41). 전 화면 62/62·플릿 108/108 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기.</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4517,6 +4517,94 @@
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>tsc·DOM 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>9.44</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SSR 회복탄력성</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>서버 fetch AbortSignal 8s + (app) 에러 바운더리 — 백엔드 장애 시 무한대기 방지</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>라이브 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9.45</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Docker 헬스체크</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>backend(/health db:true)·web-next(3000) healthy 신호</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>컨테이너 실증</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>9.46</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>변경관리대장 사이클</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>엔지니어 요청 3건 처리(단가 오늘 자동일자·요구 v0.2·1건 보류) — PM 트리아지 왕복</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>플릿 재검증 109/109</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>npm HIGH 취약점 해소</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>next 15.5.21 + overrides(postcss 8.5.23·sharp 0.35.3) — DoS/SSRF/XSS advisories</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>audit 0건·빌드 green</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4605,6 +4605,116 @@
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>audit 0건·빌드 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>9.50~9.53</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>AI 활성화 준비·배포 안정</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>ai/chat NameError·content[0].text 4곳 수정, opus-5 카탈로그·max_tokens, autodeploy 타임아웃 900→2400</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>C9 스모크 신설</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>9.55</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>U17 설계 오류조건 경고</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>저장만 되던 error_check 실평가(위반/미평가 정직 구분)+Work Process 경고 배너</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>라이브 17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>9.56</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>U19 PCR 사업유형 다열 비교</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>행=지표 8종·열=사업유형·Δ (원가 열람 모드 준수)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>라이브 13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>9.58</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>U16 실행 설정 고급</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>UI Designer 하이퍼링크 실이동·매크로 실평가(프로그램 실행은 불가 사유 명시)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>빌드 green</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>9.61~9.63</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>U20·U6·U24 잔여 해소</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>child 도면 연결·자리표시자 배치 영속(드래그)·Coding 패널 임시 식 편집</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>라이브 15/15</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (108 스위트·실 HTTP+psql, 시드 자기치유)</t>
+          <t>라이브 API 플릿 (113 스위트·실 HTTP+psql, 시드 자기치유)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 108/108</t>
+          <t>PASS 113/113</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝 전면(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31) ·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(대비/포커스/이름/키보드, 9.38~9.41). 전 화면 62/62·플릿 108/108 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기.</t>
+          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝 전면(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31) ·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(대비/포커스/이름/키보드, 9.38~9.41). 전 화면 62/62·플릿 113/113 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기.</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (113 스위트·실 HTTP+psql, 시드 자기치유)</t>
+          <t>라이브 API 플릿 (115 스위트·실 HTTP+psql, 시드 자기치유)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 113/113</t>
+          <t>PASS 115/115</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (115 스위트·실 HTTP+psql, 시드 자기치유)</t>
+          <t>라이브 API 플릿 (116 스위트·실 HTTP+psql, 시드 자기치유)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 115/115</t>
+          <t>PASS 115/115 (9.90) · 신규 116번째 스위트 단독 23/23</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>안전</t>
+          <t>조치완료(9.95)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>추적 파일 하드코딩 시크릿 0·.env/.pem/.key/oauth 미추적</t>
+          <t>추적 파일 하드코딩 시크릿 0·.env/.pem/.key/oauth 미추적. 단, 이 점검은 "커밋된 값"만 봐서 os.getenv 기본값을 놓쳤음 — 9.95 에서 EDIM_SECRET 기본값(소스 공개) 발견·차단. 이후 전 getenv 기본값 재점검, 잔여 0</t>
         </is>
       </c>
     </row>
@@ -4977,6 +4977,94 @@
       <c r="D11" s="5" t="inlineStr">
         <is>
           <t>autodeploy health-gate+자동롤백. 이번 세션 마이그레이션 전량 additive(하위호환)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>세션 토큰 서명 키</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(9.95)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>HMAC 키 기본값이 소스에 공개("edim-dev-secret")되어 ADMIN 토큰 위조 가능했고 운영도 기본 키 사용 중이었음. 운영 키 회전(openssl rand -hex 32) + 미설정 시 기동 거부(개발만 EDIM_DEV_MODE=1). .env.example·설치/관리자 문서 명문화</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>비밀번호 저장 방식</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(9.96)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>솔트·스트레칭 없는 sha256 단일 해시 → DB 유출 시 전량 복원 가능했음. PBKDF2-HMAC-SHA256 260k+계정별 솔트로 교체, 기존 해시는 로그인 시 자동 승격(일괄 재설정 불요). 유닛 21케이스·라이브 23케이스</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>계정 운영</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>비밀번호 분실 복구</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(9.97)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>복구 경로 자체가 없어 DB 직접 수정 외 방법이 없었음 → 관리자 재설정(임시 12자·잠금 동시 해제·본인 계정 409·감사 PW_RESET) 신설</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>배포 안전</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>환경변수 기본값이 외부를 가리킴</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(9.94)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>EDIM_API_BASE 미설정 시 개발 데모 도메인으로 폴백 → 고객 데이터 외부 유출 방향. 단일 출처화 + 자기 배포 내부 기본값</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (116 스위트·실 HTTP+psql, 시드 자기치유)</t>
+          <t>라이브 API 플릿 (118 스위트·실 HTTP+psql, 시드 자기치유)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 115/115 (9.90) · 신규 116번째 스위트 단독 23/23</t>
+          <t>PASS 117/117 (배포 개입 없는 실행) · 이후 이동 수정 반영 118 스위트</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (118 스위트·실 HTTP+psql, 시드 자기치유)</t>
+          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 117/117 (배포 개입 없는 실행) · 이후 이동 수정 반영 118 스위트</t>
+          <t>PASS 124/124 (중간 배포 없는 실행 · 2026-07-26)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0054_anomaly_security</t>
+          <t>0057_approval_assigned_idx</t>
         </is>
       </c>
     </row>
@@ -629,19 +629,19 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유)</t>
+          <t>라이브 API 플릿 (121 스위트·실 HTTP+psql, 시드 자기치유·잔재 자가정리)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 124/124 (중간 배포 없는 실행 · 2026-07-26)</t>
+          <t>PASS 131/131 (스위트 121 + 게이트 10종 · 중간 배포 없는 실행 · 2026-07-26)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>정적/브라우저 게이트 9종 (테넌트/커서/동사/거버넌스/FK/잔재/i18n 62화면/a11y 이름 62화면)</t>
+          <t>정적/브라우저 게이트 10종 (테넌트/커서/동사/거버넌스/FK/잔재/i18n 62화면/a11y 이름 62화면/감사 커버리지/검증 코드 문법)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝 전면(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31) ·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(대비/포커스/이름/키보드, 9.38~9.41). 전 화면 62/62·플릿 113/113 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기.</t>
+          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 18건(게이트로 증가 차단, 위험 순 축소 중).</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4715,6 +4715,226 @@
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>라이브 15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>9.95~9.97</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>인증 하드닝</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>세션 토큰 서명키 기본값 차단(운영 키 회전)·비밀번호 PBKDF2 전환(로그인 시 자동 승격)·관리자 비밀번호 재설정 신설</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>라이브 29/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>9.99</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>마지막 관리자 보호</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>강등·비활성·삭제로 관리 불능이 되는 경로 차단(과잉 차단 없음 확인)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>라이브 24/24 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>10.0~10.5</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Hierarchy 복제·이동</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>구조 복제 신설 / 이동이 하위 주소를 남기고 순환까지 만들던 결함 실증·수정</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>라이브 17/17·24/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>10.9~11.1</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>BOM 순환·정직 보고</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>간접 순환 차단(실증: B→A 201 등록) · Running Test 고정 판정→실계산 · Where-Used relId</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>라이브 25/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>구조 무결성 상시 감시</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>수동 점검이던 계층 정합을 플릿에 편입 — 실데이터 손상 조기 발견</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>라이브 14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>11.4~11.9</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>승인·원가·견적 근거</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>요청자 본인 승인 금지 정책 / 단가 미해결이 견적을 싸 보이게 만들던 경로(실운영 1건) / 견적 발행 시점 근거 스냅샷</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>라이브 18/18·29/29·23/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>12.1~12.3</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>업무 날짜·단가 대장</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>UTC/KST 불일치로 00~09시 날짜 하루 밀림(실측) / 단가 대장 데모 코드 하드코딩 필터 제거</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>라이브 14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>12.4~12.8</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>제품 스코프 일소</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Run 루트·제조비 도면·drift 재전개·치수 저장·산출물 파일명·C-1 화면의 데모 제품 하드코딩 8곳</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>라이브 15/15·11/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>13.1~13.5</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>문서 개정·승인 위임</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>DOC-001 개정 버전 자동 증가 / ADM-003 위임 + 결정자(approver_id) 기록</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>라이브 17/17·22/22</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>13.8~14.4</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>감사 추적</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>쓰기 32곳 기록 없음 → 위험 순 14곳 보강(32→18) + 커버리지 게이트·검증 코드 문법 게이트</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>라이브 21/21·게이트 2종</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5065,6 +5285,94 @@
       <c r="D15" s="7" t="inlineStr">
         <is>
           <t>EDIM_API_BASE 미설정 시 개발 데모 도메인으로 폴백 → 고객 데이터 외부 유출 방향. 단일 출처화 + 자기 배포 내부 기본값</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>감사 추적</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>쓰기 이력 기록</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(13.8~14.4)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>업무 쓰기 208개 중 32곳이 기록 없이 데이터를 바꾸고 있었다 — 위험 순 14곳 보강(32→18), 커버리지 게이트로 증가 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>승인 요청 도달 범위</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(13.8)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>알림 대상이 SETUP/ADMIN 뿐이라 PLATFORM 승인자가 빠졌다 — PLATFORM 포함 + ACTIVE 조건</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>승인 통제</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>요청자 본인 결정</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>정책 제공(11.4)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>기본 꺼짐 — 감사 요구 시 켜면 본인 결정 403, 일괄은 selfBlocked 로 별도 보고</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>데이터 정합</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>구성 순환</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(10.9/11.3)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>BOM 간접 순환 차단 + 계층 정합 상시 감시(수동 점검이라 아무도 돌리지 않던 것)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 18건(게이트로 증가 차단, 위험 순 축소 중).</t>
+          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 9건(게이트로 증가 차단, 위험 순 축소 중).</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>쓰기 32곳 기록 없음 → 위험 순 14곳 보강(32→18) + 커버리지 게이트·검증 코드 문법 게이트</t>
+          <t>쓰기 32곳 기록 없음 → 위험 순 23곳 보강(32→9) + 커버리지 게이트·검증 코드 문법 게이트</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>라이브 21/21·게이트 2종</t>
+          <t>라이브 21/21 · 게이트 2종</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>업무 쓰기 208개 중 32곳이 기록 없이 데이터를 바꾸고 있었다 — 위험 순 14곳 보강(32→18), 커버리지 게이트로 증가 차단</t>
+          <t>업무 쓰기 208개 중 32곳이 기록 없이 데이터를 바꾸고 있었다 — 위험 순 23곳 보강(32→9), 커버리지 게이트로 증가 차단. 잔여 9건은 배치·도형·UI 정의 저장(금액·판단 근거에서 한 단계 떨어짐)으로 기준선에 사유 기재</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 9건(게이트로 증가 차단, 위험 순 축소 중).</t>
+          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 7건(게이트로 증가 차단, 위험 순 축소 중).</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>쓰기 32곳 기록 없음 → 위험 순 23곳 보강(32→9) + 커버리지 게이트·검증 코드 문법 게이트</t>
+          <t>쓰기 32곳 기록 없음 → 위험 순 25곳 보강(32→7) + 커버리지 게이트·검증 코드 문법 게이트</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>라이브 21/21 · 게이트 2종</t>
+          <t>라이브 26/26 · 게이트 2종</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>업무 쓰기 208개 중 32곳이 기록 없이 데이터를 바꾸고 있었다 — 위험 순 23곳 보강(32→9), 커버리지 게이트로 증가 차단. 잔여 9건은 배치·도형·UI 정의 저장(금액·판단 근거에서 한 단계 떨어짐)으로 기준선에 사유 기재</t>
+          <t>업무 쓰기 208개 중 32곳이 기록 없이 데이터를 바꾸고 있었다 — 위험 순 25곳 보강(32→7), 커버리지 게이트로 증가 차단. CAD 저장은 덮어쓰기를 신규와 액션으로 구분. 잔여 7건은 배치·UI 정의이거나 자체 기록(author·created_by)이 있는 경로로 기준선에 사유 기재</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4935,6 +4935,28 @@
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t>라이브 26/26 · 게이트 2종</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>파일 통제 우회 차단</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>산출물 파일 다운로드가 견적·원가 Export 통제를 우회하던 문제(실증 200·25KB) + Excel Import 6곳 크기 상한 부재</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>라이브 43/43</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5373,6 +5395,50 @@
       <c r="D19" s="7" t="inlineStr">
         <is>
           <t>BOM 간접 순환 차단 + 계층 정합 상시 감시(수동 점검이라 아무도 돌리지 않던 것)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Export 통제</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>산출물 파일 직접 다운로드</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(15.1)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>no_download 상태에서 렌더 PDF 는 403 인데 같은 금액의 Run 산출물 PDF 를 /files/download 로 받을 수 있었다(실증) — 폴더→정보그룹 매핑으로 동일 통제 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>가용성</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>업로드 크기 상한</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(15.1)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Excel Import 6곳이 파일 전체를 메모리로 읽고 있었다 — 공용 헬퍼로 20MB 상한·빈 파일 거부, 초과 시 413 에 크기 병기</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4957,6 +4957,28 @@
       <c r="D64" s="2" t="inlineStr">
         <is>
           <t>라이브 43/43</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>15.3~15.4</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>세션·알림·오프보딩</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>알림 읽음 거짓 성공 수정 + 비활성화 즉시 차단 회귀 고정 + 테넌트 export 의 금액 테이블 Export 통제 적용(제외 사실 고지)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>라이브 18/18·47/47</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5439,6 +5461,28 @@
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Excel Import 6곳이 파일 전체를 메모리로 읽고 있었다 — 공용 헬퍼로 20MB 상한·빈 파일 거부, 초과 시 413 에 크기 병기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Export 통제</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>테넌트 오프보딩 export</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(15.4)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>금액 테이블(cst_quotation)이 Export 통제 없이 덤프됐다 — 해당 테이블만 제외하고 manifest·헤더·감사에 사유 기재(오프보딩 자체는 계약상 권리라 막지 않는다)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4979,6 +4979,28 @@
       <c r="D65" s="2" t="inlineStr">
         <is>
           <t>라이브 18/18·47/47</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>15.6~15.8</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>거래처 반출 통제</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>partner 그룹이 반출 0곳에 적용되던 문제 보강 + 혼합 내용은 열 마스킹으로 과잉 차단 교정</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>라이브 52/52·16/16</t>
         </is>
       </c>
     </row>
@@ -4993,7 +5015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5483,6 +5505,28 @@
       <c r="D22" s="7" t="inlineStr">
         <is>
           <t>금액 테이블(cst_quotation)이 Export 통제 없이 덤프됐다 — 해당 테이블만 제외하고 manifest·헤더·감사에 사유 기재(오프보딩 자체는 계약상 권리라 막지 않는다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Export 통제</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>거래처(partner) 반출</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>조치완료(15.6~15.8)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>마스킹 9곳 대비 반출 통제 0곳이었다 — 거래처 대장은 파일 차단, 단가·부품 대장은 공급처 열 마스킹(혼합 내용은 파일 단위로 막으면 다른 그룹의 정당한 권한을 침해)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5001,6 +5001,28 @@
       <c r="D66" s="2" t="inlineStr">
         <is>
           <t>라이브 52/52·16/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>인쇄 출력 통제</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>CAD 축척 인쇄에 파일 반출 통제 적용 + PDF 5종 전수 점검(정보그룹 7종 경로 완료)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>라이브 9/9</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5023,6 +5023,28 @@
       <c r="D67" s="2" t="inlineStr">
         <is>
           <t>라이브 9/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>16.2~16.3</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>절단 고지</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>감사 조회·통합 검색이 조용히 잘리던 문제 — truncated/hasMore 고지, LIMIT 33곳 전수 판단</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>라이브 39/39</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5045,6 +5045,28 @@
       <c r="D68" s="2" t="inlineStr">
         <is>
           <t>라이브 39/39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>16.5~16.6</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>동시 편집 보호</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>매크로 저장 낙관적 잠금 — version 컬럼이 있는데 잠금에 쓰이지 않아 계산식이 덮어써지던 문제</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>라이브 20/20</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 131/131 (스위트 121 + 게이트 10종 · 중간 배포 없는 실행 · 2026-07-26)</t>
+          <t>PASS 132/132 (스위트 122 + 게이트 10종 · 중간 배포 없는 실행 · 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5067,6 +5067,28 @@
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t>라이브 20/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>16.7~16.9</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>잠금 우회·절단 고지</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>치수 저장이 매크로 version 을 안 올려 잠금 무력화 + Run 목록 조용한 절단으로 통계 불일치</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>라이브 22/22·8/8</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5089,6 +5089,50 @@
       <c r="D70" s="2" t="inlineStr">
         <is>
           <t>라이브 22/22·8/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>승인 상태 허용 집합을 DB 에 고정</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>핵심 상태 컬럼 4개(product_code·code_relationship·code_item_value·cst_quotation)에 CHECK 제약이 없었다. 집합이 파이썬에만 있으면 잘못된 값이 저장돼도 막히지 않고, 이후 조회가 그 행을 걸러 내므로 오류가 아니라 실종으로 나타난다. 규격(승인상태기계)과 코드의 쓰기 경로를 전수로 합집합해 집합을 정했다(0058).</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>서버 실증 — 제약 4개 적용 확인, alembic_version=0058_status_check. 적용 전 실데이터 분포 확인(단일값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>거버넌스 정의서 누락 복구 + 미분류 게이트</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>문서 생성기가 alembic 리비전만 읽어 base_schema.sql 의 기준 테이블 34개가 문서에서 통째로 빠져 있었다(빈 칸이 아니라 행 자체가 없어 누락을 알 수 없는 형태). 양쪽 원본과 ALTER TABLE CHECK 까지 읽게 하고, 그때 드러난 계층 미분류 21건을 분류.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>상태흐름 29→55행 · 경계정의 53→87행 · 초기값이 실제 DEFAULT 와 일치. 게이트에 '미분류 실패' 추가 후 규칙을 되돌려 실제 실패 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5133,6 +5133,28 @@
       <c r="D72" s="2" t="inlineStr">
         <is>
           <t>상태흐름 29→55행 · 경계정의 53→87행 · 초기값이 실제 DEFAULT 와 일치. 게이트에 '미분류 실패' 추가 후 규칙을 되돌려 실제 실패 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>승인 대상의 테넌트 소유 검증</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>POST /approvals 가 targetId 를 확인 없이 받아, 다른 테넌트의 자산을 대상으로 승인 요청을 만들 수 있었다. 결정을 내리면 상대 테넌트의 상태가 실제로 전이됐다(재현 후 복구). 생성 시 소유 확인 + 반영 UPDATE 에 tenant_id 조건, 두 층위로 차단.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>live_approval_tenant 7/7 — 교차 대상 404 · 정상 경로 통과 · 미지원 대상 422. 테넌트 스코프 기준선 68→67</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5155,6 +5155,28 @@
       <c r="D73" s="2" t="inlineStr">
         <is>
           <t>live_approval_tenant 7/7 — 교차 대상 404 · 정상 경로 통과 · 미지원 대상 422. 테넌트 스코프 기준선 68→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>묵은 승인 요청의 조용한 되돌림 차단</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>미결 요청 처리 시 대상의 현재 상태를 확인하지 않아, 비활성으로 막아 둔 제품 코드가 묵은 요청 승인으로 되살아났다. 조건부 UPDATE 만 있던 분기는 0행이어도 '승인' 으로 기록되고 알림이 나갔다. 승인은 사전 확인 후 409, 반려는 요청만 닫고 자산은 건드리지 않는다.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>live_approval_stale — 비활성 대상 승인 409 · 상태 불변 · 반려는 가능 · 반려가 덮어쓰지 않음 · 원복</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>POST /approvals 가 targetId 를 확인 없이 받아, 다른 테넌트의 자산을 대상으로 승인 요청을 만들 수 있었다. 결정을 내리면 상대 테넌트의 상태가 실제로 전이됐다(재현 후 복구). 생성 시 소유 확인 + 반영 UPDATE 에 tenant_id 조건, 두 층위로 차단.</t>
+          <t>POST /approvals 가 targetId 를 확인 없이 받아, 다른 테넌트의 자산을 대상으로 승인 요청을 만들 수 있었다. 결정 반영 UPDATE 에도 테넌트 조건이 없어 그 경로 어디에도 테넌트 필터가 없다(정적 확인). 최초 보고한 실증은 계정·대상이 모두 같은 테넌트였던 잘못된 시연으로 17.8 에서 정정했다. 생성 시 소유 확인 + 반영 UPDATE 에 tenant_id 조건, 두 층위로 차단.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>live_approval_tenant 7/7 — 교차 대상 404 · 정상 경로 통과 · 미지원 대상 422. 테넌트 스코프 기준선 68→67</t>
+          <t>live_approval_tenant 8/8 — 실재하는 타 테넌트 행 대상 404 · 정상 경로 통과 · 미지원 대상 422. 테넌트 스코프 기준선 68→67</t>
         </is>
       </c>
     </row>
@@ -5177,6 +5177,50 @@
       <c r="D74" s="2" t="inlineStr">
         <is>
           <t>live_approval_stale — 비활성 대상 승인 409 · 상태 불변 · 반려는 가능 · 반려가 덮어쓰지 않음 · 원복</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>0058 CHECK 집합 누락 복구 + 검증 픽스처 정정</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>0058 에 '쓰기 경로를 전수로 모았다' 고 적었으나 code_item_value 의 DEPRECATED 를 빠뜨려 Variant 값 폐기가 500 이 됐다(dict 로 조립한 SET 절은 approval_status=%s 검색에 안 걸린다). 0059 로 복구. 이후 열거는 함수 단위로 한다. live_action_verbs 는 존재하지 않는 head_id 를 승인 대상으로 쓰고 있어 실재하는 Head 로 교체.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>플릿 live_f5_updates 가 잡음 · 함수 단위 재열거로 4개 컬럼 전량 재확인 · 단위 115/115</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>교차 테넌트 실증 주장 정정</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>17.3 에서 '테넌트1 관리자가 테넌트2 데이터를 전이시켰다' 고 보고했으나, 검증 계정 edim 은 테넌트 2 이고 대상 제품 코드 #8 도 테넌트 2 였다 — 같은 테넌트 안의 변경이었다. 결함(소유 검증 부재·테넌트 조건 부재)은 코드로 확인되지만 실행 실증은 없다. 회귀 검증도 '실재하는 타 테넌트 행' 을 쓰도록 고쳤다(종전엔 존재하지 않는 ID 일 수 있었다).</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>live_approval_tenant 8/8 — 타 테넌트 행 실재 확인 후 404</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (121 스위트·실 HTTP+psql, 시드 자기치유·잔재 자가정리)</t>
+          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 10종</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 132/132 (스위트 122 + 게이트 10종 · 중간 배포 없는 실행 · 2026-07-26)</t>
+          <t>PASS 134/134 (스위트 124 + 게이트 10종 · 중간 배포 없는 깨끗한 실행 · 2026-07-26). 승인 상태 기계 점검(17.1~17.9) 반영 — 상태 CHECK 제약, 승인 대상 소유 검증, 묵은 요청 차단 포함</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5221,6 +5221,28 @@
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t>live_approval_tenant 8/8 — 타 테넌트 행 실재 확인 후 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>잔재 게이트 진단 안내 보강</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>플릿의 유일한 실패가 잔재 게이트였는데, 잔재 증가가 아니라 앞선 실패 실행이 남긴 값을 이번 실행이 정리한 것이었다(PENDING 1→0). live_all 이 스위트 직전에 기준 지문을 저장하므로 더러운 상태로 시작하면 잔재가 기준선에 들어간다. 0 으로 줄어든 항목은 그 가능성을 함께 안내.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>DB 직접 확인 — F5T 0건 · 고아 승인요청 0건 · code_item_value 23건 전량 APPROVED. 깨끗한 상태 재실행 플릿 134/134</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5243,6 +5243,72 @@
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t>DB 직접 확인 — F5T 0건 · 고아 승인요청 0건 · code_item_value 23건 전량 APPROVED. 깨끗한 상태 재실행 플릿 134/134</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>17.10</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>인쇄·리포트 출력 통제 정합</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>출력 경로 22곳을 열람 통제와 대조. 견적 미리보기 PDF(/cpq/quote-preview.pdf)에 통제가 없어 품목 단가·견적 합계가 그대로 나갔다(저장된 견적서 PDF 는 quote, 단가 내보내기는 price 를 요구한다 — '영속 없음' 을 이유로 빠져 있었다). 감사 로그 XLSX 는 기본 1,000행에서 자르면서 X-Truncated: 0 을 돌려줬다 — 판정 기준이 EXPORT_ROW_CAP(50,000)이었기 때문.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>live_cost_masking 52→55 (미리보기 quote 403 · price 403 · full 200) · live_hardening 13/13 (X-Limit=1 · X-Truncated=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>17.11</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>검증 헬퍼 인자 수 정적 검사</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>회귀 검증을 붙일 때 ok(label, cond, detail) 형태를 2인자 헬퍼에 그대로 써서 실행 중 TypeError 로 죽었다 — 라이브 스위트는 그 전에 실 데이터를 바꿔 놓고 정리 블록도 못 돈다. check_test_syntax 에 호출 인자 수 검사를 추가.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>세 번째 인자를 되돌려 실제 FAIL(line 287 지목) 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>17.12</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>업로드 빈 파일 검사 통일 + 의존성 패치</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Import 경로 9곳 점검. 감사·테넌트는 전부 있었고 크기 검사만 두 갈래였다 — 파일 업로드·CAD Import 가 인라인 100MB 검사를 따로 갖고 있어 빈 파일 검사가 빠졌다(0바이트 첨부가 등록됨). 같은 헬퍼로 합치고 상한 초과 안내를 경로별로 맞췄다. next 15.5.22 · react 19.2.8.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>live_file_role — 빈 파일 422 · 사유 문구 · 행 미생성. npm audit 0건 · build 통과</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,24 +629,24 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 10종</t>
+          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 11종</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 134/134 (스위트 124 + 게이트 10종 · 중간 배포 없는 깨끗한 실행 · 2026-07-26). 승인 상태 기계 점검(17.1~17.9) 반영 — 상태 CHECK 제약, 승인 대상 소유 검증, 묵은 요청 차단 포함</t>
+          <t>직전 깨끗한 실행 PASS 134/134 (스위트 124 + 게이트 10종 · 2026-07-26). 이후 게이트가 11종(DB정의서 신설)이 되어 총계는 135 로 늘어난다 — 그 수치는 다음 전량 실행 결과로 갱신한다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>정적/브라우저 게이트 10종 (테넌트/커서/동사/거버넌스/FK/잔재/i18n 62화면/a11y 이름 62화면/감사 커버리지/검증 코드 문법)</t>
+          <t>정적/브라우저 게이트 11종 (테넌트/커서/동사/거버넌스/DB정의서/FK/잔재/i18n 62화면/a11y 이름 62화면/감사 커버리지/검증 코드 문법·인자수)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ALL PASS</t>
+          <t>ALL PASS — DB정의서 게이트는 18.2 신설(문서=생성기 + 스냅샷=실 스키마)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>직전 깨끗한 실행 PASS 134/134 (스위트 124 + 게이트 10종 · 2026-07-26). 이후 게이트가 11종(DB정의서 신설)이 되어 총계는 135 로 늘어난다 — 그 수치는 다음 전량 실행 결과로 갱신한다.</t>
+          <t>PASS 135/135 (스위트 124 + 게이트 11종 · 2026-07-26). 중간 배포 없음을 러너가 스스로 확인한 실행 — /health.proc 이 시작·종료 시점에 동일(18.4). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import (17.10~17.12)·DB정의서 생성 전환(18.2) 반영</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5309,6 +5309,28 @@
       <c r="D80" s="2" t="inlineStr">
         <is>
           <t>live_file_role — 빈 파일 422 · 사유 문구 · 행 미생성. npm audit 0건 · build 통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>플릿이 중간 배포를 스스로 감지</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>두 번 연속 '게이트 실패 → 단독 실행하면 통과' 를 겪었고 원인은 매번 플릿 도중 배포로 인한 컨테이너 재시작이었다(직전 90분간 7회). 문서에는 '중간 배포 없는 실행' 이라 적어 왔으나 확인 장치가 없었다. /health 에 proc(기동 시 난수) 추가, 러너가 시작·종료 시점을 비교해 다르면 초록이어도 exit 1. 실패 오탐보다 반대 경우가 위험하다 — 재시작 중 우연히 통과하면 실패했어야 할 실행이 초록으로 보인다.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>플릿 135/135 · proc 불변 확인(재시작 경고 0건 · exit 0) — 러너가 스스로 '깨끗한 실행' 을 확인한 첫 결과</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -713,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3248,6 +3248,36 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>협의</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>식별자 체계 통일 (문서 ↔ 구현)</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>협의</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>(협의/결정)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>추적성 사슬이 화면 이후로 이어지려면 필요 — 18.6 실측</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3259,7 +3289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3529,6 +3559,26 @@
       <c r="D12" s="10" t="inlineStr">
         <is>
           <t>저위험 Tenant-only (Phase2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>협의</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>식별자 체계 통일 (설계 문서 ↔ 구현)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>추적표 화면 ID 는 W-01 계열, 구현은 C-1·D-1 계열 · 메뉴 기능코드는 E-x·S-x-x, 구현 화면코드와 일치 26/89 · API 경로도 설계 108건 중 42건만 일치. 어느 쪽을 기준으로 삼을지(또는 매핑표를 확정할지) 결정 필요 — 추측으로 이으면 그럴듯한 오답이 된다. 결정 전까지 REQ→기능→메뉴→화면→컴포넌트→DB 사슬은 화면 이후가 코드로 이어지지 않는다</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,24 +629,24 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 11종</t>
+          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 12종</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 135/135 (스위트 124 + 게이트 11종 · 2026-07-26). 중간 배포 없음을 러너가 스스로 확인한 실행 — /health.proc 이 시작·종료 시점에 동일(18.4). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import (17.10~17.12)·DB정의서 생성 전환(18.2) 반영</t>
+          <t>PASS 136/136 (스위트 124 + 게이트 12종 · 2026-07-26). 중간 배포 없음을 러너가 확인한 실행(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2 DB정의서 · 18.6 API 계약) 반영</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>정적/브라우저 게이트 11종 (테넌트/커서/동사/거버넌스/DB정의서/FK/잔재/i18n 62화면/a11y 이름 62화면/감사 커버리지/검증 코드 문법·인자수)</t>
+          <t>정적/브라우저 게이트 12종 (테넌트/커서/동사/거버넌스/DB정의서/API계약/FK/잔재/i18n 62화면/a11y 이름 62화면/감사 커버리지/검증 코드 문법·인자수)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ALL PASS — DB정의서 게이트는 18.2 신설(문서=생성기 + 스냅샷=실 스키마)</t>
+          <t>ALL PASS — DB정의서(18.2)·API계약(18.6) 게이트 신설</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5381,6 +5381,28 @@
       <c r="D81" s="2" t="inlineStr">
         <is>
           <t>플릿 135/135 · proc 불변 확인(재시작 경고 0건 · exit 0) — 러너가 스스로 '깨끗한 실행' 을 확인한 첫 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>18.6~18.7</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>API 계약 as-built 전환 + 추적성 과대 주장 제거</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>컴포넌트정의서 API목록 108건 중 라우터에 그대로 있는 것은 42건(경로 상이 31·메서드 상이 9·미구현 26). 배포 app.openapi() 기준으로 생성 전환(446 오퍼레이션)하고 설계 초안은 대조 시트로 보존. 추적표 커버리지 '100%' 를 고리별 실측(요구사항→기능 100 · 기능→화면 55%)으로 교체. 구형 /api 라우터 5개는 앱 인증이 없고 nginx auth_basic 한 줄에만 의존하던 것을 불변식으로 고정.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>플릿 136/136(게이트 12종) · live_security_headers 12→17 · check_api_contract 신설</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3593,7 +3593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5403,6 +5403,28 @@
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t>플릿 136/136(게이트 12종) · live_security_headers 12→17 · check_api_contract 신설</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>18.9~18.10</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>산출물 결정성 복구 + API 표면 커버리지 실측</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>같은 Snapshot 재실행이 초 경계를 넘으면 다른 체크섬이 나왔다 — DXF 헤더의 $TDCREATE·$TDUPDATE(벽시계)가 산출물 지문에 섞여 있었다. Runtime Snapshot 계층의 전제가 실제로는 성립하지 않던 상태. 헤더 휘발성 변수 9종을 값까지 제외. 검증은 두 호출을 붙여 보내 대개 같은 초에 떨어져 운으로 통과했으므로 초 경계를 넘도록 고쳤다.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>임계 실측(gap 1.0s 불일치 → 수정 후 0·1.0·2.5s 동일, 다른 파라미터는 여전히 다름) · 수정 전 배포본에서 검증 실패 확인 · live_drawing_job 18/18 · API 커버리지 419/446(93%)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3593,7 +3593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5425,6 +5425,28 @@
       <c r="D83" s="2" t="inlineStr">
         <is>
           <t>임계 실측(gap 1.0s 불일치 → 수정 후 0·1.0·2.5s 동일, 다른 파라미터는 여전히 다름) · 수정 전 배포본에서 검증 실패 확인 · live_drawing_job 18/18 · API 커버리지 419/446(93%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>수정 불가 대화의 조용한 절단 + 미검증 쓰기 경로 보강</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>API 표면 실측(18.9)에서 플릿이 한 번도 두드리지 않는 쓰기 경로 8건이 드러났다. 그중 프로젝트 대화 등록이 1000자에서 조용히 잘렸다 — 대화는 '수정 불가' 규약이라 되돌릴 수도 없고 사용자는 잃은 줄 모른다. 초과는 422 로 거부하고 실제 자수·상한을 사유에 담는다.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>live_project_comments 20/20 — 상한 초과 422·사유의 자수·잘린 행 미생성·경계 1000자 통과 (과잉 차단 아님)·남의 글 GENERAL 403·ADMIN 삭제·삭제 감사에 원본 보존</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (124 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 12종</t>
+          <t>라이브 API 플릿 (125 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 12종</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 136/136 (스위트 124 + 게이트 12종 · 2026-07-26). 중간 배포 없음을 러너가 확인한 실행(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2 DB정의서 · 18.6 API 계약) 반영</t>
+          <t>PASS 137/137 (스위트 125 + 게이트 12종 · 2026-07-26). 중간 배포 없음을 러너가 확인(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2·18.6)·산출물 결정성(18.10)·대화 절단(18.11) 반영</t>
         </is>
       </c>
     </row>
@@ -687,16 +687,28 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>API 표면 커버리지 (실측 — 요청 로그 기준)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>422/446 (94%) · 미호출 24건 (구형 /api 5 · 읽기 전용 다수). 검증 소스의 경로 문자열이 아니라 실제 호출을 센다</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 7건(게이트로 증가 차단, 위험 순 축소 중).</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5459,6 +5459,28 @@
       <c r="D84" s="2" t="inlineStr">
         <is>
           <t>live_project_comments 20/20 — 상한 초과 422·사유의 자수·잘린 행 미생성·경계 1000자 통과 (과잉 차단 아님)·남의 글 GENERAL 403·ADMIN 삭제·삭제 감사에 원본 보존</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>18.14</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>완전성이 판단에 쓰이는 목록의 절단 고지 (개별 3회 → 헬퍼로 정리)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>조용한 절단을 개별로 세 번 고친 뒤(Run 목록·감사 JSON·감사 XLSX) 네 번째를 또 인라인으로 붙이는 대신 상한이 걸린 엔드포인트 51곳을 기계적으로 훑어 고지 없는 35곳을 뽑았고, 완전성이 판단에 쓰이는 3종에 적용했다 — 임시 열람 부여(보안 검토)·Snapshot(재현 근거)·프로젝트 대화(이력). 공통 헬퍼 _mark_truncated 로 'LIMIT cap+1 로 한 줄 더 읽어야 잘림을 안다' 는 점까지 한곳에 모았다. LIMIT 1 단건·설계상 top-N 위젯은 대상 밖(근거 기재).</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>live_hardening 13→19 · live_project_comments 20→23 — 세 목록 모두 X-Limit·X-Truncated 확인, 넉넉한 상한에서는 false</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5481,6 +5481,28 @@
       <c r="D85" s="2" t="inlineStr">
         <is>
           <t>live_hardening 13→19 · live_project_comments 20→23 — 세 목록 모두 X-Limit·X-Truncated 확인, 넉넉한 상한에서는 false</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>18.16</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>삭제 이력에 '무엇을' 지웠는지 보존</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>삭제 경로 34곳 전수 점검 — 감사는 33곳에 있었으나 30곳이 before 를 남기지 않아 '누가 #12를 지웠다' 만 남고 내용은 원본과 함께 사라졌다. 계산 근거가 되는 기준값부터 채웠다(환율·세율·공휴일·부품 대체·BOM 관계). BOM 관계는 주석이 '원가·소요량이 달라진다' 고 적어 놓고 정작 before 에 소요량이 없었다. 네 곳 모두 이미 RETURNING 으로 읽고 버리던 값이라 추가 쿼리 없이 그대로 썼다.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>live_delete_history 11/11 — 3종을 만들고 지운 뒤 before 에 값 확인, 없는 것 삭제는 404. 삭제가 곧 검증이라 잔재 0</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -629,12 +629,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (125 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 12종</t>
+          <t>라이브 API 플릿 (126 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 12종</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 137/137 (스위트 125 + 게이트 12종 · 2026-07-26). 중간 배포 없음을 러너가 확인(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2·18.6)·산출물 결정성(18.10)·대화 절단(18.11) 반영</t>
+          <t>PASS 138/138 (스위트 126 + 게이트 12종 · 2026-07-26). 중간 배포 없음을 러너가 확인(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2·18.6)·산출물 결정성(18.10)·대화 절단(18.11)·목록 절단 고지(18.14)·삭제 이력 보존(18.16) 반영</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5503,6 +5503,28 @@
       <c r="D86" s="2" t="inlineStr">
         <is>
           <t>live_delete_history 11/11 — 3종을 만들고 지운 뒤 before 에 값 확인, 없는 것 삭제는 404. 삭제가 곧 검증이라 잔재 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>18.19</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>삭제 이력 보존 확대 — 신원·권한·금액·코드</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>R-39 잔여를 위험 순으로. 사용자 삭제는 after 에 로그인만 있어 (a)삭제인데 after 를 썼고 (b)이름·등급·소속이 계정과 함께 사라졌다. 역할 삭제는 권한 행까지 지우면서 그 역할이 무엇을 할 수 있었는지 남기지 않았다. 견적은 금액이, 제품코드는 명칭·계층·승인상태가 없었다. 네 곳 모두 이미 읽고 있던 값을 버리고 있었다. 부수 — 견적 삭제 DELETE 에 테넌트 조건이 없던 것을 게이트가 잡아 기준선에 넣지 않고 조건을 추가.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>live_delete_history 11→17 — 사용자 신원(로그인·등급·이름)·역할 권한 목록 보존 확인, 검증용 계정·역할 잔재 0</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5525,6 +5525,28 @@
       <c r="D87" s="2" t="inlineStr">
         <is>
           <t>live_delete_history 11→17 — 사용자 신원(로그인·등급·이름)·역할 권한 목록 보존 확인, 검증용 계정·역할 잔재 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>18.21</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>연쇄 삭제가 지운 범위를 알린다</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>도면 삭제는 개정·승인·부품관계·Supersedure 를 함께 지우고 파일 연결까지 끊는데 응답도 감사도 도면번호 하나뿐이었다 — '개정이 몇 건이었나'를 어디에서도 알 수 없다. 단계별 rowcount 를 응답(cascade)과 감사 before 에 담는다. 문서·프로젝트 삭제도 제목·판·보안등급·고객·단계까지 남기고, after_data 로 잘못 쓰던 것을 before 로 바로잡았다. 세 곳 DELETE 에 테넌트 조건 추가(기준선 67→65).</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>live_b7_drawings 17/17 — 실측 cascade {supersedures:1, revisions:2} 확인. 리팩터로 게이트가 문장을 못 보게 된 것을 되돌림(f-string 테이블명 금지)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5547,6 +5547,28 @@
       <c r="D88" s="2" t="inlineStr">
         <is>
           <t>live_b7_drawings 17/17 — 실측 cascade {supersedures:1, revisions:2} 확인. 리팩터로 게이트가 문장을 못 보게 된 것을 되돌림(f-string 테이블명 금지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>18.23</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>삭제 이력 보존 — 수식·객체 경로·Head 유형</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>매크로 삭제가 이름만 남기고 수식을 버렸다 — 수식은 계산 규칙 그 자체이고 치수·검증·구성 join 이 이 식을 근거로 돈다. 파일 삭제는 스토리지 객체까지 지우면서 어떤 경로였는지·객체를 지웠는지 기록이 없었다. Head 는 권한 임계 필드인 headType 이 빠져 있었다. 셋 다 after 로 잘못 쓰던 것을 before 로 바로잡았고, 매크로 DELETE 에 테넌트 조건 추가(기준선 65→64).</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>live_delete_history 17→20 — 매크로 수식(=A*2+7)·상태·버전·참조 삭제 건수 보존 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5569,6 +5569,28 @@
       <c r="D89" s="2" t="inlineStr">
         <is>
           <t>live_delete_history 17→20 — 매크로 수식(=A*2+7)·상태·버전·참조 삭제 건수 보존 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>삭제 이력 보존 — 부품·창고·Templet·견적안</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>부품은 번호만 남기고 이름·규격과 함께 지운 공급자 코드 매핑 건수(조달 경로)가 없었다. 견적안은 완성품 코드만 남겼는데 슬롯 선택값이 곧 그 견적안의 내용이다(같은 코드라도 슬롯이 다르면 다른 제품). 창고·Templet 도 이름/코드만 있었다. 넷 다 after 를 before 로 바로잡고 DELETE 에 테넌트 조건 추가(기준선 64→62).</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>live_delete_history 20→23 — 창고 이름·유형 보존 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5591,6 +5591,28 @@
       <c r="D90" s="2" t="inlineStr">
         <is>
           <t>live_delete_history 20→23 — 창고 이름·유형 보존 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>18.27</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Import 거부 사유가 DB 예외를 그대로 내보내던 문제</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>오류 응답 경로 점검 — 단가 Import 한 곳만 str(e)[:80] 로 DB 예외를 거부 리포트에 실었다. 제약명·테이블 같은 내부 구조가 나가고, 사용자는 무엇을 고쳐야 할지 알 수 없다(다른 Import 4종은 이미 사람이 읽을 사유를 쓴다). 기간중복·중복·참조없음·필수누락·형식오류로 분류하고 원문은 구조화 로그로 서버에만 남긴다. /macros/graph 의 파서 메시지는 사용자 수식에 대한 설명이라 대상 아님.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>live_g3_bulk_import 8→11 — 같은 기간 재등록으로 EXCLUDE 위반을 실제 유발해 사유가 '기간 중복' 으로 나오고 constraint·SQL 키워드가 없음을 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5613,6 +5613,28 @@
       <c r="D91" s="2" t="inlineStr">
         <is>
           <t>live_g3_bulk_import 8→11 — 같은 기간 재등록으로 EXCLUDE 위반을 실제 유발해 사유가 '기간 중복' 으로 나오고 constraint·SQL 키워드가 없음을 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>18.29</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>수정 이력에 '무엇에서' 를 담는다</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>삭제와 같은 방식으로 수정(PUT/PATCH) 48곳 점검 — 감사 43곳 중 before 는 13곳뿐이었다. 매크로 저장·치수 저장은 주석이 '어떻게 바뀌었는지 남긴다'고 적어 놓고 새 값/건수만 남겼다. 정보접근 모드는 열람 통제 자체를 바꾸는 조작인데 이전 모드가 없었다. 제품코드 승인 상태도 마찬가지. 매크로는 치수 저장 경로로도 수식이 바뀌므로 두 곳을 함께 고쳐야 이력 사슬이 이어진다.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>live_delete_history 23→27 — 수식 =A+1→=A+2 전후 보존, 정보접근 masked→full 이전 모드 보존</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5635,6 +5635,28 @@
       <c r="D92" s="2" t="inlineStr">
         <is>
           <t>live_delete_history 23→27 — 수식 =A+1→=A+2 전후 보존, 정보접근 masked→full 이전 모드 보존</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>18.31</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>수정 이력 — 계정 활성 전환·공정 정의</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>계정 활성/비활성은 새 상태만 남아 이전에 이미 그 상태였는지도, 등급도 알 수 없었다(존재 확인 조회를 분기 밖으로 꺼내 중복 조회도 제거). 공정 정의는 주석이 '제조비 산정 입력' 이라 적고 건수만 남겼다 — 어떤 공정이 MAKE→BUY 로 바뀌었는지 모르면 제조비 변동에 답할 수 없다. documents/status 는 from/to 를 이미 담고 있어 대상 아님(스캔 오탐 2건째).</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>live_delete_history 27→30 — 비활성화 이력에 이전 상태(ACTIVE)·등급(GENERAL) 보존</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5657,6 +5657,28 @@
       <c r="D93" s="2" t="inlineStr">
         <is>
           <t>live_delete_history 27→30 — 비활성화 이력에 이전 상태(ACTIVE)·등급(GENERAL) 보존</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>18.33~18.34</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>수정 이력 — 발주 승인 금액·테넌트 요금제·Head 권한 임계값</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>정보 완전성 기준으로 재선별한 20건 중 상위 3곳. 발주 승인은 금액 확정 행위인데 발주번호만 남았고, 테넌트 요금제·상태는 계약·차단에 직결되며, Head 상태·min_level 은 권한 임계값이다. 구현 중 erp_po 에 없는 금액 컬럼을 가정해 500 이 났고(스키마 스냅샷 미확인 3회째) 라인아이템 합계로 교체. 그 과정에서 erp_po 행이 0개 — 구조화 발주 lifecycle 이 한 번도 호출된 적 없음이 드러났다.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>live_b19_warehouse 20→23 — 발주 생성→승인 후 이력에 승인 시점 합계(4,500)·라인수·이전 상태(DRAFT) 보존 확인. 기준선 62→61</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5679,6 +5679,50 @@
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t>live_b19_warehouse 20→23 — 발주 생성→승인 후 이력에 승인 시점 합계(4,500)·라인수·이전 상태(DRAFT) 보존 확인. 기준선 62→61</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>18.36</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>설계 검증이 사실상 항상 합격이던 문제</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>커버리지 실측에서 한 번도 호출된 적 없는 경로로 잡혀 검증을 붙이자 드러났다. 판정 규약은 '매크로 값이 0 이 아니면 통과' 인데 시드가 치수 매크로(=A+56, =A*1.62)를 규칙으로 붙여, K 8,100(한계 1,500)도 합격이었다. 경고 문구가 약속한 임계값 검사가 수행되지 않았다. 판정 전용 매크로(&lt;=900, &lt;=1500)로 교체 — 치수 매크로는 다른 역할이라 그대로 둔다. 시드만으로는 기존 데이터가 안 바뀌어 alembic 0060 으로 함께 바로잡음(downgrade 는 의도적 공백).</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>live_design_verify 10/10 신설 — 한계 초과 불합격(fail 2/2)·경계값 통과·한 규칙만 위반해도 불합격(1/2)·경고 문구 부착</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>18.37</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>마이그레이션 실패가 배포 성공으로 보이던 문제</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>0060 이 ON CONFLICT 추론 불일치(tbx_macro UNIQUE 는 name+version)로 롤백됐는데, lifespan 이 예외를 로그로만 남기고 앱을 띄우므로 /health 는 ok, 배포 게이트도 통과했다 — 코드와 스키마가 어긋난 채 운영된다. 가용성 설계는 유지하고 상태를 드러낸다: /health 에 schema head|error|unknown.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>live_security_headers 17→19 — schema 필드 존재 + head 확인. 운영 실측 {'status':'ok','db':true,'schema':'head'} · alembic 0060 적용</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5723,6 +5723,28 @@
       <c r="D96" s="2" t="inlineStr">
         <is>
           <t>live_security_headers 17→19 — schema 필드 존재 + head 확인. 운영 실측 {'status':'ok','db':true,'schema':'head'} · alembic 0060 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>18.39</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>블록도 형상이 조용히 잘리던 문제</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>커버리지 미호출 목록의 두 번째 경로. blocks[:500]·dims/labels[:200] 로 조용히 잘랐다 — 목록 절단과 달리 도면은 잘려도 완성된 도면처럼 보이고, 빠진 형상으로 제작이 진행되면 실물이 달라진다. 상한 초과는 그리지 않고 422 로 개수·상한을 알린다(부분 도면보다 안 내놓는 편이 안전). 미호출 목록에서 고른 두 경로가 모두 결함을 갖고 있었다.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>live_cad_blocks 8/8 신설 — 상한 초과 422·사유의 개수(501)/상한(500)·경계값 500 통과·.dxf 응답이 실제 DXF</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5745,6 +5745,28 @@
       <c r="D97" s="2" t="inlineStr">
         <is>
           <t>live_cad_blocks 8/8 신설 — 상한 초과 422·사유의 개수(501)/상한(500)·경계값 500 통과·.dxf 응답이 실제 DXF</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>18.41</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>수정 이력 — 프로젝트 단계·Contract 선언</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>영업 단계 전이는 사업 진행 상태 그 자체이고 납기일 변경은 일정 약속이 바뀐 것인데 새 값만 남았다. 바뀐 필드만 before 에 담는다(안 바꾼 값까지 넣으면 대조가 흐려진다). Contract 는 '어떤 원천의 어떤 필드를 쓸 수 있는지' 선언하는 통제라 이전 선언이 남아야 허용 필드 증가를 확인할 수 있다 — 신규 등록은 before 에 그 사실을 명시해 빈 값과 구분.</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>live_delete_history 30→32 — 프로젝트 수정 이력에 이전 값 보존. 기준선 62→61</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5767,6 +5767,28 @@
       <c r="D98" s="2" t="inlineStr">
         <is>
           <t>live_delete_history 30→32 — 프로젝트 수정 이력에 이전 값 보존. 기준선 62→61</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>18.43</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>수정 이력 마무리 — 설계 파라미터·로트 유효기한·문서 채번 규칙</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>설계 우선순위·기준점·오류조건은 도면 해석과 원가 계산의 입력인데 건수만 남았다(치수 저장과 같은 형태라 함께 맞춤). 유효기한은 출하 가능 여부를 가르므로 이전 기한이 없으면 '연장' 과 '최초 설정' 을 구분할 수 없다. 채번 규칙은 문서번호 체계 자체다. R-41 을 14종으로 종결하고 잔여 12곳은 대상 아님 근거를 기재(비밀번호·이미 완전한 from/to·UI 표시 상태·이동 경로에 이력 존재).</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>게이트 전량 통과 · 테넌트 기준선 62→61</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5789,6 +5789,28 @@
       <c r="D99" s="2" t="inlineStr">
         <is>
           <t>게이트 전량 통과 · 테넌트 기준선 62→61</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>규정만 있고 구현이 없던 Idempotency-Key 구현</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>개발표준 §3 이 '생성 계열은 Idempotency-Key 지원' 을 규정하는데 코드에 문자열조차 없었다. 운영 실측: 같은 요청 4회(그중 2회 같은 키) → 원가 실적 4행 — 재시도·더블클릭이 그대로 원가 이중 계상이었다. sys_idempotency(0061) + 키 선점 방식 구현. 작업 후 저장하면 동시 요청 둘 다 조회를 빗나가 둘 다 실행되므로 먼저 잡는다. 우선 적용: 원가 실적(이중 계상)·임시 열람 부여(중복 부여 시 하나 회수해도 나머지가 남는다). 헤더는 선택이라 기존 동작 불변.</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>live_idempotency 10/10 신설 — 같은 키 2회에 행 1건·idempotentReplay·다른 키는 별개</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5811,6 +5811,28 @@
       <c r="D100" s="2" t="inlineStr">
         <is>
           <t>live_idempotency 10/10 신설 — 같은 키 2회에 행 1건·idempotentReplay·다른 키는 별개</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>18.47~18.48</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>문서 드리프트 게이트가 내 누락을 잡음 + 멱등성 확대</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>18.45 에서 새 테이블(sys_idempotency)을 만들고 문서를 재생성하지 않아 check_governance·check_db_dict 가 실패했다 — 18.2·18.6 에서 이 게이트를 만든 목적 그대로다(문서가 코드보다 뒤처지는 것을 사람이 기억할 필요가 없게). 멱등성은 발주(중복은 실제 손해)·QCR(공급자에게 두 번 나가고 회신도 두 벌)·Rev-up(재시도가 Rev 를 한 칸 더 올린다)으로 확대.</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>live_idempotency 10→14 — Rev-up 응답과 DB current_rev 양쪽 확인(C→D 한 칸)·원복. DB정의서 108테이블/1,189컬럼/354제약 · 거버넌스 상태흐름 56</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5833,6 +5833,50 @@
       <c r="D101" s="2" t="inlineStr">
         <is>
           <t>live_idempotency 10→14 — Rev-up 응답과 DB current_rev 양쪽 확인(C→D 한 칸)·원복. DB정의서 108테이블/1,189컬럼/354제약 · 거버넌스 상태흐름 56</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>18.51~18.53</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정이 열린 세션을 끊지 않던 문제</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>운영 실측 — 관리자 재설정 후 옛 비밀번호 로그인은 401 인데 옛 토큰 조회는 200(최대 8시간). 재설정은 계정 탈취 표준 대응인데 이미 열린 세션을 끊지 못했다. 비활성화는 매 요청 즉시 반영되는데(15.3) 같은 목적의 다른 경로만 빠져 있었다. sys_user.pw_changed_at(0062) + require_auth 에서 발급 시각(exp-TTL) 비교. 기존 계정은 NULL 로 두어 이미 로그인한 사용자를 끊지 않는다. 판정은 초 단위 — 토큰 발급 시각이 초로 잘려 있어 정밀 비교하면 변경 직후 발급한 토큰이 자기 변경 시각에 걸린다(18.52).</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>live_session_notify 20→26 — 재설정 후 401·사유 명시·재로그인. 검증은 초 경계를 넘겨 확인한다(붙여 호출하면 구현이 보장하지 않는 것을 요구하게 된다 — 18.53)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>18.54</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>[사고] 본인 비밀번호 변경이 세션을 끊어 데모 계정 잠김 — 복구·되돌림</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>18.51 에서 본인 변경도 세션을 끊게 했다. 새 토큰을 응답에 담았으나 **기존 클라이언트는 그 토큰을 쓰지 않고 원래 토큰으로 다음 호출을 한다** → 401. live_security 의 비밀번호 되돌리기가 실패했고 이후 스위트들이 옛 비밀번호로 반복 로그인해 edim 계정이 LOCKED(플릿 130/141). 복구 후 본인 변경은 갱신하지 않도록 되돌렸다 — 탈취 대응은 관리자 재설정이 담당하고, 본인이 아는 비밀번호를 바꾸는 것은 그 목적이 아니다. 다른 기기 세션까지 끊으려면 프런트가 새 토큰을 받아 쓰도록 선행 변경이 필요하다.</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>복구 실증 — edim 로그인 200·ACTIVE, live_session_notify 26/26 · live_security 27/27 · 플릿 141/141</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5877,6 +5877,138 @@
       <c r="D103" s="2" t="inlineStr">
         <is>
           <t>복구 실증 — edim 로그인 200·ACTIVE, live_session_notify 26/26 · live_security 27/27 · 플릿 141/141</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>18.55</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>파일 다운로드 경로 조작 점검 — 해당 없음</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>download_file 은 사용자 입력이 아니라 DB 의 file_path 를 테넌트 조건과 함께 읽어 저장소에 넘긴다. 업로드 폴더도 화이트리스트(DWG/PRICE/DATA/BOM/RECEIVED)라 임의 폴더를 만들지 못한다.</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>코드 확인 + 업로드 폴더 422 응답 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>18.56</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>저장소 키에 테넌트 성분 없음 — 교차 테넌트 덮어쓰기 가능 경로 식별</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>키가 {project}/{folder}/{name} 인데 프로젝트 번호는 테넌트별 유니크라 두 테넌트가 같은 번호를 갖는다(PS-61313-5 가 양쪽). 업로드 가드(#53)는 tenant_id 조건 조회라 남의 객체를 보지 못한다. 현재 충돌 0건인 것은 테넌트1 의 옛 /edim/ 접두사 덕이지 통제가 아니다.</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>운영 DB 분포 확인(테넌트1 3건·테넌트2 4,760건) · 공유 경로 0건 — 덮어쓰기 실행 실증은 하지 않음(정적 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>18.57</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>저장소 키 테넌트 이름 공간 분리</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>_storage_key(tid,…) 로 신규 키를 t{tid}/ 아래에 두고 Run 산출물(persist_outputs)도 동일. 기존 행은 저장 경로를 그대로 써 마이그레이션 없이 열린다. #53 가드는 신·구 두 경로를 함께 조회하고, 옛 경로 행이면 경로를 유지해 행이 갈라지지 않게 한다.</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>live_storage_ns 14/14 · 기존 파일 다운로드 200/5,390B · 신규 Run 1581 산출물 3건 t2/ 적재·다운로드 200/18,514B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>18.58</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>없는 프로젝트 업로드를 조용한 고아 대신 422 로 거부</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>업로드·CAD 반입·도면 저장 4곳이 prj[0] if prj else None 로 project_id 를 NULL 로 넣고 201 을 돌려줬다. 성공했는데 어느 프로젝트 폴더에도 없는 상태. 운영 NULL 행 0건이라 거부해도 잃는 동작이 없다. 검사는 put_object 앞으로 옮겨 고아 객체를 남기지 않는다.</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>live_storage_ns — 업로드 422·도면저장 422·행 0건·project_id NULL 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>18.59</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>/files 가 project 인자를 쓰지 않던 문제 — 프로젝트 간 산출물 노출</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Run 산출물 구간이 project 를 아예 쓰지 않아 어느 프로젝트를 열든(없는 번호 포함) 테넌트 최신 Run 산출물이 나왔다. cpq_output→cpq_run→cpq_selection→prj_project 로 묶고 최신 Run 판정도 프로젝트 단위로 내렸다. 업로드 구간의 OR project_id IS NULL 도 제거.</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>운영 실측(4개 질의에서 앞 3건 동일) → 수정 후 live_storage_ns 에서 프로젝트별 산출물·업로드 수가 DB 와 일치, 없는 프로젝트 422</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>18.60</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>미사용 라우트 인자 게이트 (check_unused_params)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>@router.* 함수의 인자가 본문 어디에도 나타나지 않으면 실패. 18.59 유형(인자를 받고 쿼리에 넣지 않음)의 재발을 막는다. 한계: 완전한 누락만 잡고 '엉뚱하게 쓴다'는 못 잡는다.</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>18.59 이전 상태 사본에서 edim.py::project_files::project 탐지 확인 · 현재 기준선 0항목</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6009,6 +6009,50 @@
       <c r="D109" s="2" t="inlineStr">
         <is>
           <t>18.59 이전 상태 사본에서 edim.py::project_files::project 탐지 확인 · 현재 기준선 0항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>18.62</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>모르는 필터 값을 조용히 버리던 3곳 — 빈 값과 모르는 값을 구분</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>/anomalies(status·source)는 모르는 값이면 조건을 붙이지 않고 전체를 돌려줬고, /arrangements(forCode)는 없는 코드를 '제품군 없음'으로 스코프했으며, /cost/variance(project)는 없는 프로젝트에 0 분석표를 돌려줬다. 빈 값=전체 보기는 유지하고 모르는 값만 422.</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>필터 GET 63개 중 48건 실측(4건 동일 → 3건 결함) · live_filter_honesty 신규(고친 3곳 + 필터 25쌍 광역 회귀, 건너뛴 건수 출력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>18.63</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>GC 가 다른 테넌트의 객체를 지울 수 있던 문제</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>/files/gc 는 테넌트 ADMIN 권한인데 버킷은 공유다. 18.57 이전엔 소유를 판별할 단서가 없어 전역으로 훑었고, 이제 t{tid}/ 접두사가 있으므로 남의 접두사 객체는 대상에서 뺀다. 접두사 없는 옛 객체는 종전대로 둔다(없는 근거로 지우거나 남기지 않는다). foreignSkipped 로 몇 건을 뺐는지 응답에 드러낸다.</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>수정 전 실증 — t9999/ 프로브 객체를 orphan 1건으로 잡고 sampleOrphans 에 노출(apply=true 면 삭제) → 수정 후 orphans 0·foreignSkipped 1 (live_storage_ns)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6053,6 +6053,94 @@
       <c r="D111" s="2" t="inlineStr">
         <is>
           <t>수정 전 실증 — t9999/ 프로브 객체를 orphan 1건으로 잡고 sampleOrphans 에 노출(apply=true 면 삭제) → 수정 후 orphans 0·foreignSkipped 1 (live_storage_ns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>18.64</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>죽은 pid 의 플릿 락 회수 + 종료코드 판독 정정</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>플릿 강제 종료 시 atexit 가 돌지 않아 락이 남고 40분간 모든 실행이 거부됐다(검증이 통째로 건너뛰어짐). 락의 pid 생존을 확인해 죽었으면 회수하고 회수 사실을 출력한다. 아울러 파이프(| tail)로 부르면 tail 의 종료코드를 보게 되어 ABORT(2)를 0으로 읽던 호출 방식을 고쳤다.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>죽은 락(pid=22212, 1412s 전) 회수 후 플릿 정상 진행 확인 · 이후 함대는 파일 리다이렉트 + $? 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>18.65</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>마스킹된 금액이 화면에서 ₩0/₩NaN 으로 찍히던 문제</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>서버는 full=숫자·masked=문자열·hidden=null 로 주는데 화면 10곳이 각자 won(v ?? 0) 로 찍었다. hidden→₩0(그럴듯한 값), masked→₩NaN. lib/money.ts(won·sumMoney·sortMoney)로 통일하고 마스킹 필드 타입을 Money 로 넓혔다. 가려진 값이 섞인 합계는 성립하지 않으므로 null→'••••'.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>tsc --noEmit 통과 · 재고/원가실적/발주/수주/대시보드 적용 · live_dashboard_masking</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>18.66</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>/erp/analytics 가 정보그룹 통제에 닿지 못하던 문제</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>누적 원가·추이·차이분석·월별 기여마진이 마스킹 없이 나갔다. request 인자가 없어 열람 모드를 물어볼 수단 자체가 없었다. cost/quote 그룹 적용. 수정 중 발생시킨 커서 결과셋 무효화(8.6)는 check_cursor_reuse 가 배포 전에 차단.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>live_dashboard_masking — cost=hidden·quote=masked 로 켜서 확인 후 원복. 기본은 full 이라 평소엔 가려지지 않음(주장 범위 명시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>18.67</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>대시보드 '이번 달 수주' 하드코딩(₩ 8.4억) 제거</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>견적/수주 모듈 구축 전 고정값이 남아 화면 맨 위에서 지어낸 숫자가 실적처럼 보였다. cst_quotation(ORDERED, 당월) 실집계 + 건수 병기 + quote 통제 적용.</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>live_dashboard_masking — 고정값 부재·quote 통제 준수·건수 표기 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6141,6 +6141,116 @@
       <c r="D115" s="2" t="inlineStr">
         <is>
           <t>live_dashboard_masking — 고정값 부재·quote 통제 준수·건수 표기 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>18.68</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>이상 출처 화이트리스트를 DB CHECK 제약과 일치</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>sys_anomaly.source 제약에는 SECURITY 가 있는데 조회 필터 목록에는 없었다. 모르는 값이면 조건을 버리던 종전 동작 탓에 ?source=SECURITY 가 전체를 돌려줬고 검증은 결과가 빌 때만 봐서 못 알아챘다. ANOMALY_SOURCES 상수로 고정.</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>플릿 143/144 로 노출(422 전환 덕에 가시화) → 다섯 값 전부 200 검증 추가 · live_security_anomaly 13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>18.69</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>발주 금액을 서버가 집계 — 마스킹 사용자의 틀린 발주서 방지</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>구매 화면이 (단가×수량) 을 합산해 보내고 서버가 그 값을 발주서 제목에 적었다. 원가 마스킹 사용자는 가려진 값으로 더하므로 0K/NaN 발주서가 생긴다. 서버가 유효 단가에서 직접 집계하고 클라이언트 값은 무시. 단가 미등록으로 제외된 품목은 응답·제목·이력에 노출.</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>tsc 통과 · 화면 금액 계산 제거 · 서버 집계값 응답(totalK·unpricedCodes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>18.70</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>입고 쓰기 응답의 원가 마스킹 (같은 데이터, 다른 경로)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>POST /erp/stock/inbound 가 평단가·평가액·자동결정 단가를 마스킹 없이 돌려줬다. 조회 경로는 9.37 에서 이미 가렸는데 쓰기 응답만 남아 있었다. avgPrice·value 는 항상, unitPrice 는 자동 결정된 경우에만 가린다(사용자가 적은 값은 제외). /prices/resolve 위젯의 화면 표기도 공용 포맷터로 교체.</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>tsc 통과 · live_dashboard_masking 확장 예정 · 화면 3곳(재고 입고 메시지·모바일 미리보기·단가 해석)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>18.71</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>쓰기 응답 전수 점검 — 읽기는 가리고 쓰기는 안 가리던 3곳</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>POST/PUT/PATCH 반환 사전에서 금액성 키를 뽑아 _mask_num 없는 17건을 추려 실제 금액 3건을 확인: POST /cost/pcr(revenue·directCostTotal·contributionMargin·ebit), POST /cost/quotations(subtotal·tax·total), POST /erp/stock/inbound. 조회와 같은 그룹 적용 + 화면 포맷터 교체.</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>정적 전수 추출(17건 후보→3건 결함) · tsc 통과 · live_dashboard_masking 확장 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>18.72</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>BOM 삭제 이력에 내용 기록 + 검증 프로브 정리 결함</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>플릿에서 dwg_bom 4→3 이 잡혔으나 감사가 {bomId, drawing} 만 남겨 어느 부품이 빠졌는지 알 수 없었다(원인 스위트 미확정). 삭제 전에 partNo·partName·itemNo·qty·assemblySeq·assemblyNote 를 before_data 에 기록. 함께 live_wiring_actions 가 '아무 부품'을 골라 쓰고 자기가 만든 실행에서만 지우던 것을 전용 프로브 상시 사용·상시 회수로 교정.</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>seed_heal 로 BOM 4행 원복 · 잔존 프로브 부품 삭제 · check_live_residue 22항목 지문 일치</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>추적표 화면 ID 는 W-01 계열, 구현은 C-1·D-1 계열 · 메뉴 기능코드는 E-x·S-x-x, 구현 화면코드와 일치 26/89 · API 경로도 설계 108건 중 42건만 일치. 어느 쪽을 기준으로 삼을지(또는 매핑표를 확정할지) 결정 필요 — 추측으로 이으면 그럴듯한 오답이 된다. 결정 전까지 REQ→기능→메뉴→화면→컴포넌트→DB 사슬은 화면 이후가 코드로 이어지지 않는다</t>
+          <t>추적표 화면 ID 는 W-01 계열, 구현은 C-1·D-1 계열 · 메뉴 기능코드는 E-x·S-x-x, 구현 화면코드와 일치 26/89 · API 경로도 설계 108건 중 42건만 일치. 어느 쪽을 기준으로 삼을지(또는 매핑표를 확정할지) 결정 필요 — 추측으로 이으면 그럴듯한 오답이 된다. 결정 전까지 REQ→기능→메뉴→화면→컴포넌트→DB 사슬은 화면 이후가 코드로 이어지지 않는다 · **영향 실측(18.73)**: 수주 라인은 변형 코드(ECC 55-32), 마스터·재고는 기준 코드(ECC 55)라 MRP 재고 대조가 수요 8건 전부 실패 → 계획이 늘 '전 품목 발주 필요'로 나온다. 구매요청 화면(/erp/pr-items)도 이 결정 전에는 실수요로 전환할 수 없어 데모 3건 고정이다.</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6251,6 +6251,28 @@
       <c r="D120" s="2" t="inlineStr">
         <is>
           <t>seed_heal 로 BOM 4행 원복 · 잔존 프로브 부품 삭제 · check_live_residue 22항목 지문 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>18.73</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>MRP 재고 대조 불가를 '보유 0'으로 보고하던 문제</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>수주 라인은 변형 코드(ECC 55-32), 마스터·재고는 기준 코드(ECC 55)라 on_hand.get(code,0) 이 늘 0 이 됐다. 실측: 수요 8건 전부 보유 0·부족 8건인데 창고에는 실재고 존재. 코드 매칭 규칙은 식별자 체계 결정(#81) 사안이라 정하지 않고, 대조 불가를 UNMATCHED(onHand·shortage=null)로 구분해 건수를 응답·화면에 노출.</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>운영 실측 8/8 미대조 확인 · tsc 통과 · MrpGrid 대조불가 칩·컬럼 '—' 표기</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>추적표 화면 ID 는 W-01 계열, 구현은 C-1·D-1 계열 · 메뉴 기능코드는 E-x·S-x-x, 구현 화면코드와 일치 26/89 · API 경로도 설계 108건 중 42건만 일치. 어느 쪽을 기준으로 삼을지(또는 매핑표를 확정할지) 결정 필요 — 추측으로 이으면 그럴듯한 오답이 된다. 결정 전까지 REQ→기능→메뉴→화면→컴포넌트→DB 사슬은 화면 이후가 코드로 이어지지 않는다 · **영향 실측(18.73)**: 수주 라인은 변형 코드(ECC 55-32), 마스터·재고는 기준 코드(ECC 55)라 MRP 재고 대조가 수요 8건 전부 실패 → 계획이 늘 '전 품목 발주 필요'로 나온다. 구매요청 화면(/erp/pr-items)도 이 결정 전에는 실수요로 전환할 수 없어 데모 3건 고정이다.</t>
+          <t>추적표 화면 ID 는 W-01 계열, 구현은 C-1·D-1 계열 · 메뉴 기능코드는 E-x·S-x-x, 구현 화면코드와 일치 26/89 · API 경로도 설계 108건 중 42건만 일치. 어느 쪽을 기준으로 삼을지(또는 매핑표를 확정할지) 결정 필요 — 추측으로 이으면 그럴듯한 오답이 된다. 결정 전까지 REQ→기능→메뉴→화면→컴포넌트→DB 사슬은 화면 이후가 코드로 이어지지 않는다 · **영향 실측(18.73)**: 수주 라인은 변형 코드(ECC 55-32), 마스터·재고는 기준 코드(ECC 55)라 MRP 재고 대조가 수요 8건 중 5건 실패 → 그 5건이 근거 없이 '부족'으로 계획된다. 구매요청 화면(/erp/pr-items)도 이 결정 전에는 실수요로 전환할 수 없어 데모 3건 고정이다.</t>
         </is>
       </c>
     </row>
@@ -6267,12 +6267,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>수주 라인은 변형 코드(ECC 55-32), 마스터·재고는 기준 코드(ECC 55)라 on_hand.get(code,0) 이 늘 0 이 됐다. 실측: 수요 8건 전부 보유 0·부족 8건인데 창고에는 실재고 존재. 코드 매칭 규칙은 식별자 체계 결정(#81) 사안이라 정하지 않고, 대조 불가를 UNMATCHED(onHand·shortage=null)로 구분해 건수를 응답·화면에 노출.</t>
+          <t>수주 라인은 변형 코드(ECC 55-32), 마스터·재고는 기준 코드(ECC 55)라 on_hand.get(code,0) 이 조용히 0 이 됐다. 실측: 수요 8건이 모두 보유 0·부족으로 보고됐고, 계기를 붙여 보니 그중 5건은 대조 자체가 불가능했다(3건은 마스터에 있는 코드로 실제 재고 0). 코드 매칭 규칙은 식별자 체계 결정(#81) 사안이라 정하지 않고, 대조 불가를 UNMATCHED(onHand·shortage=null)로 구분해 건수를 응답·화면에 노출.</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>운영 실측 8/8 미대조 확인 · tsc 통과 · MrpGrid 대조불가 칩·컬럼 '—' 표기</t>
+          <t>live_mrp_match 9/9 신규(그전까지 MRP 검증 0건) — 미대조 5/8 확인 · 재고를 넣으면 UNMATCHED→SHORT 로 대조되고 부족=소요−보유 일치 · 실증 재고 정리</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6273,6 +6273,28 @@
       <c r="D121" s="2" t="inlineStr">
         <is>
           <t>live_mrp_match 9/9 신규(그전까지 MRP 검증 0건) — 미대조 5/8 확인 · 재고를 넣으면 UNMATCHED→SHORT 로 대조되고 부족=소요−보유 일치 · 실증 재고 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>18.74</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>재고 '단가 미등록'과 '통제로 가려짐'·'실제 0원' 을 구분</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>입고 시 단가 미지정 + cst_price(STOCK) 부재면 단가가 0 으로 남는데, 화면은 가려짐·미등록·실제 0원을 모두 ₩0 으로 찍었다. 응답에 priced 를 더해 미등록을 구분하고, 화면은 '미등록'·'—' 로 표기하며 총 평가액에서 제외한 뒤 제외 종수를 함께 표시.</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 8화면 실측(JS 오류 0) — 대시보드 실값·MRP 대조불가 5 확인, 재고 총 평가액 ₩0 만 잔여였고 그 원인을 해소</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6295,6 +6295,28 @@
       <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Playwright 8화면 실측(JS 오류 0) — 대시보드 실값·MRP 대조불가 5 확인, 재고 총 평가액 ₩0 만 잔여였고 그 원인을 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>[회귀] 공용 금액 포맷터가 null 의 뜻을 뭉갠 것 교정</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>18.65 에서 화면 10곳의 won() 을 공용화하며 null→'••••'(가려짐)로 일괄 처리했는데, 구매 화면의 null 은 '재고 충족이라 단가 미조회', PCR 의 null 은 '미산출' 이었다. stockOk 로 분기하고, maskMode 를 보는 wonBy() 를 추가해 full+null 은 '—', 그 밖은 '••••' 로 구분. 나머지 호출 지점은 null 이 마스킹에서만 나오는지 개별 확인.</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>배포본 Playwright 재확인에서 발견 · tsc 통과 · 구매/PCR 화면 표기 교정</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6317,6 +6317,28 @@
       <c r="D123" s="2" t="inlineStr">
         <is>
           <t>배포본 Playwright 재확인에서 발견 · tsc 통과 · 구매/PCR 화면 표기 교정</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>18.76</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>파일 묶음 상한 부재·누락 무고지 해소</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>/files/zip 은 미호출 경로였다. 프로젝트 하나가 4,990건·79MB 인데 상한 없이 메모리에서 압축했고, 저장소에서 못 받은 객체는 조용히 건너뛰며 아무것도 알리지 않았다. 상한(1,000건·200MB) 초과는 잘라 주지 않고 413 거부(사유에 실제 규모·분할 안내), 누락은 X-Missing 헤더와 묶음 안 _누락파일.txt 로 고지. 고객 전달본도 동일 상한.</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>live_zip_bounds 14/14 신규 — 전체 413 · DATA 폴더 200 · 없는 객체 행 삽입 시 X-Missing 1·누락 메모·파일명 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6339,6 +6339,50 @@
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t>live_zip_bounds 14/14 신규 — 전체 413 · DATA 폴더 200 · 없는 객체 행 삽입 시 X-Missing 1·누락 메모·파일명 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>18.77</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>고객 전달 패키지에 과거 Run 산출물이 전부 담기던 문제</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>종전엔 프로젝트의 DELIVER_FOLDERS 파일을 전부 담아 DWG·PRICE 각 1,654건(Run 마다 한 벌)이었다. 같은 견적서·도면이 Run 수만큼 중복돼 고객에게 나간다. 최신 SUCCESS Run 산출물 + 작도 원본만 담도록 변경하고 매니페스트에 포함·제외 명시.</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>실측 4,987건 → 68건(워터마크 11) · live_zip_bounds 18/18 (전달본이 전체보다 작고 산출물이 한 Run 것만인지 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>컬럼 영속 검증의 고정 대기 제거 (제품 아닌 검증 결함)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>live_g2_colprefs 가 플릿·단독 모두 실패했으나 원인은 새로고침 직후 prefs 를 비동기로 적용하는 것을 400ms 고정 대기로 읽은 것. 서버 저장 확인 + 화면 반영 대기로 교체. 조사 중 저장 버킷(gridColWidths/gridColOrder)과 prefKey(next-audit)를 두 번 오인 — 저장값을 직접 확인해 교정.</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>3회 연속 7/7 통과 · 저장값 {'at': 217} 및 순서 배열 실측 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6383,6 +6383,28 @@
       <c r="D126" s="2" t="inlineStr">
         <is>
           <t>3회 연속 7/7 통과 · 저장값 {'at': 217} 및 순서 배열 실측 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>18.79</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>다운로드 프록시가 오류 사유를 버리던 문제</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>/api/next/bin 이 실패 시 {detail:'HTTP 413'} 만 반환해 백엔드가 적은 사유(상한 초과·Export 권한 거부 등)가 사라졌다. 문서 PDF·PCR·파일·CAD 플롯·ZIP 전 경로가 이 프록시를 지난다. detail 통과로 수정하고, Project Folder ZIP 버튼은 새 탭(window.open) 대신 받아서 내려받거나 사유를 화면에 표시.</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>live_zip_bounds 20/20 — 화면에 상한 사유 원문 표시 확인 · 전달 패키지 정상 다운로드 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3301,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3591,6 +3591,28 @@
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>추적표 화면 ID 는 W-01 계열, 구현은 C-1·D-1 계열 · 메뉴 기능코드는 E-x·S-x-x, 구현 화면코드와 일치 26/89 · API 경로도 설계 108건 중 42건만 일치. 어느 쪽을 기준으로 삼을지(또는 매핑표를 확정할지) 결정 필요 — 추측으로 이으면 그럴듯한 오답이 된다. 결정 전까지 REQ→기능→메뉴→화면→컴포넌트→DB 사슬은 화면 이후가 코드로 이어지지 않는다 · **영향 실측(18.73)**: 수주 라인은 변형 코드(ECC 55-32), 마스터·재고는 기준 코드(ECC 55)라 MRP 재고 대조가 수요 8건 중 5건 실패 → 그 5건이 근거 없이 '부족'으로 계획된다. 구매요청 화면(/erp/pr-items)도 이 결정 전에는 실수요로 전환할 수 없어 데모 3건 고정이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>테스트 Run 취급 범위 · Run 산출물 보존 기간</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>① 테스트로 표시한 Run 을 원가 기준(PCR·견적·차이분석)에서도 제외할지 — 현재는 사실만 표시하고 숫자는 그대로 둔다(18.80). ② Run 산출물 보존 기간 — 정리(cleanup)는 Run 메타만 지우고 파일은 보존해 무기한 누적된다(데모 실측 5,071건·80MB, 그중 테스트 Run 분 2,283건·36MB). 삭제 가능 여부는 산출물 불변(#53) 원칙과 함께 결정 필요.</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6405,6 +6427,28 @@
       <c r="D127" s="2" t="inlineStr">
         <is>
           <t>live_zip_bounds 20/20 — 화면에 상한 사유 원문 표시 확인 · 전달 패키지 정상 다운로드 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>18.80</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>테스트 Run 이 전달본·원가 기준이 되던 문제</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>cpq_run.is_test 가 통계에서만 제외돼, 최신 SUCCESS 가 테스트 Run 이면 그 산출물이 고객 전달본에 담기고 PCR·견적·차이분석의 원가 기준이 됐다(운영에서 해당 Run 확인). 전달본은 NOT is_test 로 차단, 원가 기준은 basisRunId·basisIsTest 와 사유 문구로 사실만 노출(정책 결정 필요 사항으로 분리).</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>live_b18_cost 22/22 (basisIsTest true·사유 확인) · live_zip_bounds 22/22 (전달 산출물 is_test=f 확인)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3627,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6449,6 +6449,28 @@
       <c r="D128" s="2" t="inlineStr">
         <is>
           <t>live_b18_cost 22/22 (basisIsTest true·사유 확인) · live_zip_bounds 22/22 (전달 산출물 is_test=f 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>18.81</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>전달본 기준 Run 명시 — 검증의 규칙 복제 제거</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>검증이 '전달본에 담기는 Run' 판정을 위해 서버 선택 규칙을 SQL 로 복제해 뒀다가 18.80(NOT is_test) 변경과 어긋나 거짓 실패를 냈다. 서버가 X-Basis-Run 헤더와 매니페스트 '기준 Run: #N' 으로 근거를 밝히고, 검증은 그 값을 읽어 업무 Run 여부만 확인한다. 받는 사람도 어느 실행의 산출물인지 알 수 있다.</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>live_zip_bounds 23/23 — 헤더·매니페스트 일치, 기준 Run is_test=f, 담긴 산출물 중 테스트 Run 0건</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3627,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6471,6 +6471,28 @@
       <c r="D129" s="2" t="inlineStr">
         <is>
           <t>live_zip_bounds 23/23 — 헤더·매니페스트 일치, 기준 Run is_test=f, 담긴 산출물 중 테스트 Run 0건</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>18.82</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Project Folder 목록 상한·절단 고지 + 현재 Run 구분</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>업로드 구간 쿼리에 LIMIT 이 없어 한 프로젝트 5,156행을 매 조회마다 전량 전송했다(Run 마다 증가). 상한 500 + X-Truncated/X-Limit 헤더와 화면 상한 칩 적용. 아울러 지난 Run 산출물이 현재 납품물과 같은 '산출물' 표기로 섞여 구분되지 않던 것을 run·currentRun 노출과 '현재' 칩으로 해소.</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>실측 5,156행 → 503행(500+최신 Run 3) · X-Truncated true · 현재 Run 3건만 표시 · live_storage_ns 36/36</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3627,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D130"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6493,6 +6493,28 @@
       <c r="D130" s="2" t="inlineStr">
         <is>
           <t>실측 5,156행 → 503행(500+최신 Run 3) · X-Truncated true · 현재 Run 3건만 표시 · live_storage_ns 36/36</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>18.83</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>목록 상한의 절단 기준 교정 — 최신순이 중요한 파일을 지우던 문제</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>18.82 상한이 최신순이라 500행이 전부 최근 Run 산출물로 채워져 시드 접수자료가 잘려 나갔다(플릿 실패로 발각). 기준을 '접수자료·작도 원본 전부 + 산출물은 현재 Run 것만'으로 바꾸고 숨김 건수를 X-Superseded-Hidden 로 고지. 교정 중 두 번 과하게 숨김(Run 미연결 산출물·기준 Run 없는 프로젝트) → 저장 경로 run{id} 표식과 '현재 없으면 지난 것도 없다'로 되돌림. Run 산출물 구간에도 상한 적용.</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>PS-61313-5 73행(숨김 5,163)·PS-598 216행·PS-612 0행 · allRuns=true 1,000행 절단 고지 · live_f1_project 30/30 · live_storage_ns 36/36</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3627,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6515,6 +6515,28 @@
       <c r="D131" s="2" t="inlineStr">
         <is>
           <t>PS-61313-5 73행(숨김 5,163)·PS-598 216행·PS-612 0행 · allRuns=true 1,000행 절단 고지 · live_f1_project 30/30 · live_storage_ns 36/36</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>18.84</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>숨김·절단 사실을 화면까지 전달</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>18.83 의 숨김 건수를 헤더로만 알려 화면에 닿지 않았다(18.79 와 같은 실수를 내 변경에 반복). apiServer 가 헤더를 버리는 구조라 SSR 이 접근할 수 없었던 것이 원인 — apiServerWith 추가. Project Folder 에 '지난 Run 산출물 숨김 N' 칩·전체/현재 Run 전환·'표시 상한 도달' 칩 표시.</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>기본 73건+숨김 5,202 표시 · 전체 1000건+상한 칩 · JS 오류 0 · live_storage_ns 40/40</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3627,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6537,6 +6537,28 @@
       <c r="D132" s="2" t="inlineStr">
         <is>
           <t>기본 73건+숨김 5,202 표시 · 전체 1000건+상한 칩 · JS 오류 0 · live_storage_ns 40/40</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Run 정리가 보존되는 산출물을 알리지 않던 문제 + 커버리지 표현 정정</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>cleanup 이 Run 1,445건을 지웠다고만 알리고 산출물 5,466건·85MB 가 그대로인 사실은 말하지 않았다(납품물 불변 #53로 보존). retainedFiles·retainedBytes·사유 문구 추가. 아울러 모든 산출물이 소속 Run 판별 근거(cpq_output 링크 또는 저장 키 run{id} 표식)를 갖는지 불변식으로 확인. measure_api_coverage 의 '검증이 두드린 표면' 표현은 실제로 창 안 전체 요청이므로 정정.</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>live_run_retention 9/9 신규(그전까지 정리 경로 검증 0건) — 응답 대조·Run 감소분 일치·파일 보존·판별 근거 0건 누락</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3301,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3612,7 +3612,29 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>① 테스트로 표시한 Run 을 원가 기준(PCR·견적·차이분석)에서도 제외할지 — 현재는 사실만 표시하고 숫자는 그대로 둔다(18.80). ② Run 산출물 보존 기간 — 정리(cleanup)는 Run 메타만 지우고 파일은 보존해 무기한 누적된다(데모 실측 5,071건·80MB, 그중 테스트 Run 분 2,283건·36MB). 삭제 가능 여부는 산출물 불변(#53) 원칙과 함께 결정 필요.</t>
+          <t>① 테스트로 표시한 Run 을 원가 기준(PCR·견적·차이분석)에서도 제외할지 — 현재는 사실만 표시하고 숫자는 그대로 둔다(18.80). ② Run 산출물 보존 기간 — 정리(cleanup)는 Run 메타만 지우고 파일은 보존해 무기한 누적된다(데모 실측 5,071건·80MB, 그중 테스트 Run 분 2,283건·36MB). 삭제 가능 여부는 산출물 불변(#53) 원칙과 함께 결정 필요. · **실측(18.86)**: Run 1회 = 산출물 3파일 ≈ 48KB (1,836 Run / 5,508 파일 / 86MB, MinIO 객체 5,558). Run 이력을 1,495건 정리해도 파일은 그대로였다 — 정리는 메타만 지운다. 월 1,000 Run 이면 연 약 0.6GB, 월 10,000 Run 이면 연 약 5.8GB 증가로 환산된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>감사 이력(sys_history) 보존 기간·보관 방식</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>**실측(18.86)**: sys_history 가 105,655행·34MB 로 **DB 전체 68MB 의 절반**이다(행당 약 342B). 보존 기간·아카이브 정책이 없어 무기한 증가한다. 최다 동작은 LOGIN_OK 29,278건(28%) — 로그인마다 1행이 쌓인다. 현재 증가율(일 16,000~34,000행)은 검증 트래픽이 대부분이라 운영 예측치는 아니지만, 사용자 수 × 로그인 빈도에 비례해 운영에서도 최대 증가 요인이 된다. 결정 필요: ① 보존 기간(법정/계약 요건) ② 기간 경과분 처리(삭제/콜드 아카이브) ③ LOGIN_OK 같은 고빈도 이벤트를 별도 보존 기간으로 둘지.</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6559,6 +6581,28 @@
       <c r="D133" s="2" t="inlineStr">
         <is>
           <t>live_run_retention 9/9 신규(그전까지 정리 경로 검증 0건) — 응답 대조·Run 감소분 일치·파일 보존·판별 근거 0건 누락</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18.86</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>데이터 증가 실측 — 결정 항목에 수치 부착</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>#82 가 '무기한 누적'이라고만 적혀 판단 근거가 없었다. 실측: Run 1회=3파일≈48KB(1,836 Run/5,508 파일/86MB), sys_history 105,655행·34MB로 DB 68MB 의 절반(행당 342B, LOGIN_OK 28%). 감사 보존은 법정·계약 요건이 걸려 개발이 정할 수 없으므로 결정 항목 #83 신설.</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>테이블·객체 크기, 일자별 증가, 동작별 분포 실측 · 위험 R-51 · 증가율은 검증 트래픽이 대부분이라 운영 예측치 아님을 명시</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3649,7 +3649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6603,6 +6603,28 @@
       <c r="D134" s="2" t="inlineStr">
         <is>
           <t>테이블·객체 크기, 일자별 증가, 동작별 분포 실측 · 위험 R-51 · 증가율은 검증 트래픽이 대부분이라 운영 예측치 아님을 명시</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18.87</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>감사 조회 facet 의 전수 스캔 제거 (본 조회의 100배 비용)</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>본 조회는 인덱스로 0.6ms 인데 필터 드롭다운 두 질의가 Seq Scan(action 49.8ms·login_id 61.8ms, 105,639행)이었다. 사용자 목록은 사용자 대장에서 얻고, 동작 목록은 alembic 0063 인덱스 + loose index scan(재귀 CTE)으로 행 수가 아닌 값 종류에 비례하게 바꿈(33.7ms→1.7ms).</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>EXPLAIN ANALYZE 실측 · live_run_retention 14/14(Seq Scan 부재·인덱스 사용·사용자 출처 확인)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3649,7 +3649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6625,6 +6625,28 @@
       <c r="D135" s="2" t="inlineStr">
         <is>
           <t>EXPLAIN ANALYZE 실측 · live_run_retention 14/14(Seq Scan 부재·인덱스 사용·사용자 출처 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>18.88</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>복구 리허설이 파일 백업을 검증하지 않던 문제</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>리허설이 DB 덤프만 열고 tables/tenants/codes 만 확인한 뒤 REHEARSAL OK 를 찍었다. 납품물은 전부 MinIO 에 있어 DB 만 복구하면 파일 행이 가리키는 바이트가 없다. 같은 날짜 tar 존재·열림·복원 DB 의 file_path 무작위 20건 대조까지 확인하도록 강화하고 판정을 DB·파일 둘 다로 변경.</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>REHEARSAL OK — dbFiles=4335 minioObjects=4320 sampled=20 missing=0 · 실패 경로 실증(tar 제거 시 FAIL·exit 1, 즉시 원복)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3301,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3635,6 +3635,28 @@
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>**실측(18.86)**: sys_history 가 105,655행·34MB 로 **DB 전체 68MB 의 절반**이다(행당 약 342B). 보존 기간·아카이브 정책이 없어 무기한 증가한다. 최다 동작은 LOGIN_OK 29,278건(28%) — 로그인마다 1행이 쌓인다. 현재 증가율(일 16,000~34,000행)은 검증 트래픽이 대부분이라 운영 예측치는 아니지만, 사용자 수 × 로그인 빈도에 비례해 운영에서도 최대 증가 요인이 된다. 결정 필요: ① 보존 기간(법정/계약 요건) ② 기간 경과분 처리(삭제/콜드 아카이브) ③ LOGIN_OK 같은 고빈도 이벤트를 별도 보존 기간으로 둘지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>백업 파이프라인 이중화 정리 여부</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>**실측(18.89)**: 같은 데이터를 두 경로로 매일 백업 중 — systemd 03:20 → /var/backups/edim(24MB) · cron 03:30 → /home/seekers/backups(27MB), 각 7일 보존. 복구 리허설은 03:20 산출물만 검증한다. 결정 필요: ① 둘을 유지할지(중복 보관의 안전성 vs 저장·관리 비용) ② 유지한다면 두 번째도 리허설 대상에 넣을지 ③ 하나로 줄인다면 어느 쪽을 남길지(형식이 다르다 — plain SQL gzip vs pg_dump -Fc). 지우는 쪽 결정은 데이터 보호와 직결돼 개발이 임의로 정하지 않았다.</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6647,6 +6669,28 @@
       <c r="D136" s="2" t="inlineStr">
         <is>
           <t>REHEARSAL OK — dbFiles=4335 minioObjects=4320 sampled=20 missing=0 · 실패 경로 실증(tar 제거 시 FAIL·exit 1, 즉시 원복)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>18.89</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>실 구동 백업 스크립트의 저장소 편입 + 이중 파이프라인 명시</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>실제 주 백업(systemd 03:20 → /var/backups/edim)이 서버에만 있고 저장소에 없었다 — 서버 재구축 시 소실. 저장소에 있던 것은 cron 03:30(/home/seekers/backups) 두 번째 파이프라인이었다. 같은 데이터를 하루 두 벌 보관 중(24MB+27MB, 각 7일). 구동본을 tools/edim-backup.sh 로 편입하고 두 스크립트 헤더에 스케줄·경로·리허설 검증 대상 명시. 통합은 운영 결정이라 보류.</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>systemd/cron 스케줄·산출물·용량 실측 · 리허설 검증 대상이 03:20 산출물뿐임을 문서화</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3301,7 +3301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3657,6 +3657,28 @@
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>**실측(18.89)**: 같은 데이터를 두 경로로 매일 백업 중 — systemd 03:20 → /var/backups/edim(24MB) · cron 03:30 → /home/seekers/backups(27MB), 각 7일 보존. 복구 리허설은 03:20 산출물만 검증한다. 결정 필요: ① 둘을 유지할지(중복 보관의 안전성 vs 저장·관리 비용) ② 유지한다면 두 번째도 리허설 대상에 넣을지 ③ 하나로 줄인다면 어느 쪽을 남길지(형식이 다르다 — plain SQL gzip vs pg_dump -Fc). 지우는 쪽 결정은 데이터 보호와 직결돼 개발이 임의로 정하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>PITR·파일 버전닝 도입 여부 · 원격지 백업 보관</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>**실측(18.90)**: 보안관리계획서가 백업 수단으로 적어 둔 PITR(WAL 아카이빙)과 파일 스토리지 버전닝이 **둘 다 미구현**이다(`archive_mode=off`·`wal_level=replica`, MinIO 버킷 versioning 미설정). 일 1회 전체 덤프로 RPO 24h·RTO 4h 목표 자체는 충족하지만, ① 임의 시점 복구 불가(전날 백업 시점으로만) ② 덮어써진 객체는 전날 백업까지만 되돌림 ③ 백업이 **원본과 같은 호스트**에만 있어 호스트 소실 시 백업도 함께 잃는다. 결정 필요: PITR 도입 여부, 버킷 versioning 활성화 여부, 원격지(오프사이트) 보관 여부.</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6691,6 +6713,28 @@
       <c r="D137" s="2" t="inlineStr">
         <is>
           <t>systemd/cron 스케줄·산출물·용량 실측 · 리허설 검증 대상이 03:20 산출물뿐임을 문서화</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>18.90</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>보안관리계획서의 백업 수단 기술을 실측과 일치</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>문서가 'DB 일 1회 + PITR, 파일 스토리지 버전닝'을 백업 수단으로 적었으나 PITR(archive_mode=off)과 MinIO 버킷 versioning 모두 미구현이었다. 실제 구현(일 1회 덤프×2 경로·파일 tar·7일 보존·주간 리허설)과 그 한계(임의 시점 복구 불가·덮어쓴 객체는 전날까지·원격지 보관 없음)를 사실대로 기술하고 결정 항목 #85 신설. 설치배포매뉴얼의 같은 문구도 정정.</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>archive_mode/wal_level·버킷 versioning 실측 · RPO 24h 충족·복원 실측 30초로 RTO 여유 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3693,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6735,6 +6735,28 @@
       <c r="D138" s="2" t="inlineStr">
         <is>
           <t>archive_mode/wal_level·버킷 versioning 실측 · RPO 24h 충족·복원 실측 30초로 RTO 여유 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>18.91</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>오프보딩 export 에 제품 구성 자산 추가 (13→22종)</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Code Set-up 마스터(code_group·code_item·code_item_value)가 통째로 빠져 제품 코드는 나가는데 그 코드를 만드는 규칙은 나가지 않았다. BOM·단가·Macro·치수·Arrangement·파일 목록도 부재. 9종 추가(dwg_bom 은 도면 경유로 테넌트 좁힘, 단가는 cost 통제 유지), 매니페스트에 파일 원본 채널과 files.json 대조표 안내 추가.</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>live_tenant_export 20/20 신규 — 포함 여부·DB 건수 일치(code_groups 3·values 23·macros 7·files 5,659)·민감 필드 부재·통제 시 단가만 제외 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -1079,10 +1079,14 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Finish</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>부분 (협의 대기)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>18.92 실측 — **계약 게이트만 구현**: 테넌트 status(ACTIVE/SUSPENDED/TERMINATED)로 로그인 차단(1.3, live_platform_tenant 검증). **Feature Entitlement 와 Quota 는 미구현** — sys_tenant.plan 은 저장·표시만 되고 게이팅에 쓰이지 않으며, 사용자수·프로젝트수·용량·AI 사용량 상한 코드가 없다. 무엇을 제한할지는 SaaS 계약 조건(#75)이 정해져야 구현 가능 — #75 에 종속된 항목이다.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3504,7 +3508,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>사용자수·용량·Project·AI사용량·Edition</t>
+          <t>사용자수·용량·Project·AI사용량·Edition · **종속 항목(18.92)**: 요구 #11 Feature Entitlement·Quota 가 이 결정에 막혀 있다 — 무엇을 몇 개까지 허용할지(사용자수·프로젝트·용량·AI 사용량·Edition)가 정해져야 게이트를 구현한다. 현재는 계약 상태(SUSPENDED/TERMINATED) 로그인 차단만 동작하고 플랜별 차등·상한은 없다.</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6757,6 +6761,28 @@
       <c r="D139" s="2" t="inlineStr">
         <is>
           <t>live_tenant_export 20/20 신규 — 포함 여부·DB 건수 일치(code_groups 3·values 23·macros 7·files 5,659)·민감 필드 부재·통제 시 단가만 제외 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>18.92</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>요구 #11(Entitlement·Quota) 상태를 실측과 일치</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>'Feature Entitlement/License Gate·Quota' 가 Finish 였으나 실측 결과 계약 게이트(테넌트 status 로 로그인 차단)만 구현돼 있었다. sys_tenant.plan 은 저장·표시만 되고 게이팅에 쓰이지 않으며 사용자수·프로젝트·용량·AI 사용량 상한 코드가 없다. 상태를 '부분(협의 대기)'로 정정하고 근거를 비고에 기재, SaaS 계약 조건(#75) 종속임을 양쪽에 명시.</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>코드 전수 검색(entitlement/license/quota 무결과) · plan 사용처가 목록·생성·수정뿐임 확인 · 계약 게이트는 live_platform_tenant 로 검증됨</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3697,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6783,6 +6783,28 @@
       <c r="D140" s="2" t="inlineStr">
         <is>
           <t>코드 전수 검색(entitlement/license/quota 무결과) · plan 사용처가 목록·생성·수정뿐임 확인 · 계약 게이트는 live_platform_tenant 로 검증됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>18.93</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>MFA 상시 검증 신설 (미호출 경로 점검 — 결함 없음)</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>요구 #10 MFA·로그인 감사가 Finish 였고 API 실측에서 /users/me/mfa 계열이 미호출 경로로 잡혀 끝까지 밟았다. setup→틀린 코드 거부→활성화→OTP 없는 로그인 차단(mfaRequired, 토큰 미발급)→틀린 OTP 401+LOGIN_MFA_FAIL 감사→맞는 OTP 로그인→해제 복귀까지 전부 정상. 결함 없음을 확인하고 상시 검증으로 고정.</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>live_mfa 14/14 신규 — 전용 프로브 계정 생성·삭제(실 계정 잠금 방지) · TOTP 를 검증 측에서 독립 구현해 서버 구현과 대조</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3697,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6805,6 +6805,28 @@
       <c r="D141" s="2" t="inlineStr">
         <is>
           <t>live_mfa 14/14 신규 — 전용 프로브 계정 생성·삭제(실 계정 잠금 방지) · TOTP 를 검증 측에서 독립 구현해 서버 구현과 대조</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>18.94</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>PCR 생성·수정 감사 누락 해소 (예외 목록 7→6)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>감사 예외 목록이 '금액·판단 근거에서 한 단계 떨어져 있다'는 한 줄 사유 아래 POST /cost/pcr 를 담고 있었으나 PCR 은 견적 확정의 근거 금액이다. cst_pcr 이력 132건이 전부 MASKED_READ 로, 변경 기록이 전무했다. upsert 전 이전 값을 읽어 before/after 로 남기고 금액의 근거(기준 Run·테스트 여부·미해결 건수·마진율)를 함께 기록.</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>배포 후 실측 — UPDATE 이력에 before(직접원가·기여마진·EBIT·상태)·after(+basisRunId·basisIsTest·unpricedCount) 확인 · 게이트 기준선 6건</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3697,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6827,6 +6827,28 @@
       <c r="D142" s="2" t="inlineStr">
         <is>
           <t>배포 후 실측 — UPDATE 이력에 before(직접원가·기여마진·EBIT·상태)·after(+basisRunId·basisIsTest·unpricedCount) 확인 · 게이트 기준선 6건</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>18.95</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>임시 열람의 시간 만료 실증 (회수와 별개 조건)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Masking·Temporary Access(P0) 점검 — 구현은 견고했다(만료·회수 조건 모두 조회 시 적용, 상한 720시간, 사유 필수, 중복 방지 멱등). 다만 검증은 회수(revoked)만 밟고 시간 만료(valid_to)는 밟지 않았다. 두 조건은 서로 달라 한쪽만 확인하면 다른 쪽이 열린 채 남을 수 있다. 만료 시각을 과거로 둔 부여를 직접 넣어 효력 없음을 확인하고, 유효한 창 대조군으로 '만료 때문' 임을 갈랐다.</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>live_info_access 16→18 — 만료된 부여 무효·유효 창 대조군 통과, 검증 데이터 잔존 0</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3697,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6849,6 +6849,28 @@
       <c r="D143" s="2" t="inlineStr">
         <is>
           <t>live_info_access 16→18 — 만료된 부여 무효·유효 창 대조군 통과, 검증 데이터 잔존 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>18.96</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>사용자 등급 변경 경로의 PLATFORM 허용 불일치 해소</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>생성 경로는 PLATFORM 을 422 로 막는데 변경 경로는 LEVEL_RANK 전체를 허용했다. 권한 상승 여부를 확인한 결과 아님 — 플랫폼 API 는 등급이 아니라 운영 테넌트 여부로 막힌다(고객사에서 PLATFORM 을 달아도 열리지 않고, 운영 테넌트에선 ADMIN 이면 이미 통과). 다만 화면상 최상위로 보이고 향후 user_level 을 권한 신호로 쓰면 구멍이 되므로 두 경로 계약을 일치. PLATFORM 사용자 0명이라 영향 없음.</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>live_f2_users 31→33 (변경 422·정상 변경 대조군·원복) · _platform_guard 의 tenant_code 검사 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3697,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6871,6 +6871,28 @@
       <c r="D144" s="2" t="inlineStr">
         <is>
           <t>live_f2_users 31→33 (변경 422·정상 변경 대조군·원복) · _platform_guard 의 tenant_code 검사 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>승인 동시 결정 경합 실증 (결함 없음·상시 검증 신설)</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Approval 상태기계(P0) 점검 — 결정이 원자적 조건부 UPDATE(WHERE result IS NULL RETURNING)라 코드상 안전해 보였으나, 채번 경합(9.18·9.19) 전례대로 실제로 동시에 눌러 확인. 동시 6건 중 성공 1건·나머지 404, 승인 행에 결정 한 벌, 자산 전이 이력 1건, 상태 1회 전이.</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>live_approval_race 7/7 신규 — 스레드 6개 동시 decide, 결과 [404,404,404,200,404,404] · ZZRACE 잔존 0</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -130,6 +130,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -520,7 +523,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -629,19 +632,19 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (126 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 12종</t>
+          <t>라이브 API 플릿 (139 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 13종</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 138/138 (스위트 126 + 게이트 12종 · 2026-07-26). 중간 배포 없음을 러너가 확인(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2·18.6)·산출물 결정성(18.10)·대화 절단(18.11)·목록 절단 고지(18.14)·삭제 이력 보존(18.16) 반영</t>
+          <t>PASS 152/152 (스위트 139 + 게이트 13종 · 2026-07-28). 중간 배포 없음을 러너가 확인(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2·18.6)·산출물 결정성(18.10)·대화 절단(18.11)·목록 절단 고지(18.14)·삭제 이력 보존(18.16) 반영</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>정적/브라우저 게이트 12종 (테넌트/커서/동사/거버넌스/DB정의서/API계약/FK/잔재/i18n 62화면/a11y 이름 62화면/감사 커버리지/검증 코드 문법·인자수)</t>
+          <t>정적/브라우저 게이트 13종 (테넌트/커서/동사/거버넌스/DB정의서/API계약/FK/잔재/i18n 62화면/반출통제/a11y 이름 62화면/감사 커버리지/검증 코드 문법·인자수)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3697,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6893,6 +6896,72 @@
       <c r="D145" s="2" t="inlineStr">
         <is>
           <t>live_approval_race 7/7 신규 — 스레드 6개 동시 decide, 결과 [404,404,404,200,404,404] · ZZRACE 잔존 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>18.98</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>폴더 일괄 ZIP 의 반출 통제 누락 (요구 #6)</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>파일을 내주는 엔드포인트 17개 전수 대조에서 /files/zip 만 통제가 없었다(Request 인자조차 없어 사용자를 볼 수 없었다). 실증 — quote·cost 를 no_download 로 두자 전달 패키지는 403 인데 ?folder=PRICE 는 견적서 83건 1,942,745바이트, BOM 은 376KB 를 그대로 내줬다. 폴더별 정보그룹 게이트 적용(폴더 미지정 시 통제 대상 전부).</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>live_cost_masking 55→59 (폴더 지정·미지정 차단, 도면 폴더 허용·ADMIN full 200 대조군) · check_download_guard 게이트 신설(통제 밖 13건 항목별 사유 기재)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>18.99</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>요구 #3 의 EXECUTE 동사 실효화 + 게이트 자체 결함 2건</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>동사 다섯(생성·수정·실행·승인·배포) 중 실효는 APPROVE·DEPLOY 뿐이었다. BOM Run·Macro 평가·Running Test 에 EXECUTE 적용(미설정=허용이라 기존 테넌트 무영향). check_verb_guard 가 ast.FunctionDef 만 보아 async 핸들러 11개를 8.10 이래 미검사, _verbs 정규식이 하이픈 자원키를 인식하지 못하던 것 동시 수정. _action_allowed 의 '설정 있음' 판정에서 화면 매트릭스 READ(MENU) 제외.</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>live_action_verbs 41→47 (화면 READ 로는 안 잠김·동사 READ 만이면 403·부여 후 통과·Macro 동일) · 게이트 규칙 C 신설</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="inlineStr">
+        <is>
+          <t>OTP 연속 실패의 계정 잠금 누락 (알림과 실제의 어긋남)</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="inlineStr">
+        <is>
+          <t>자동 잠금 카운터가 LOGIN_FAIL 만 세어 2단계 실패는 임계에 들어가지 않았다 — 비밀번호를 아는 공격자에게 남는 방어가 분당 30회 속도 제한뿐이었다. 이상 탐지기는 두 실패를 함께 세어 '연속 N회 (잠금 임계 5)' 라고 알리고 있어, 화면과 실제가 어긋난 상태이기도 했다. _auth_fail_streak() 로 기준을 하나로 모았다.</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>live_mfa 14→23 (임계까지 실제 두드려 LOCKED·잠긴 뒤 맞는 OTP 도 403·관리자 해제 후 복귀)</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7419,6 +7488,72 @@
       <c r="D23" s="7" t="inlineStr">
         <is>
           <t>마스킹 9곳 대비 반출 통제 0곳이었다 — 거래처 대장은 파일 차단, 단가·부품 대장은 공급처 열 마스킹(혼합 내용은 파일 단위로 막으면 다른 그룹의 정당한 권한을 침해)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Export 통제</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>폴더 일괄 ZIP(/files/zip)</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>조치완료(18.98)</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>한 건 다운로드·전달 패키지는 막히는데 폴더 일괄 ZIP 만 통제가 없었다(Request 인자 부재). no_download 상태에서 견적서 83건 1.9MB 반출 실증 → 폴더별 정보그룹 게이트 적용. 재발 방지로 check_download_guard 게이트 신설(반출 경로 전수 대조, 예외 13건 항목별 사유).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>작업 권한</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>실행(EXECUTE) 동사</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>조치완료(18.99)</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>요구 #3 동사 다섯 중 APPROVE·DEPLOY 만 실효했다. BOM Run·Macro 평가·Running Test 에 EXECUTE 적용. 정적 게이트가 async 핸들러 11개를 미검사하던 것과 하이픈 자원키 미인식도 동시 수정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>인증</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2단계(OTP) 실패의 계정 잠금</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>조치완료(19.0)</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>잠금 카운터가 비밀번호 실패만 세어 OTP 는 무제한 시도 가능했다(방어는 분당 30회 속도 제한뿐). 이상 탐지기는 두 실패를 함께 세어 '잠금 임계 5' 로 알리던 어긋남도 함께 해소 — 두 실패를 함께 세는 단일 기준으로 통일.</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6962,6 +6962,72 @@
       <c r="D148" s="11" t="inlineStr">
         <is>
           <t>live_mfa 14→23 (임계까지 실제 두드려 LOCKED·잠긴 뒤 맞는 OTP 도 403·관리자 해제 후 복귀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>계약 게이트를 매 요청 재확인으로 확장</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>PATCH /platform/tenants 는 'SUSPENDED/TERMINATED 는 즉시 로그인 차단' 이라고 적혀 있었지만 sys_tenant.status 를 읽는 곳은 로그인 경로 한 곳뿐이었다 — 중지 시점에 발급된 토큰이 최대 8시간 유효했다. 인증 의존성에서 테넌트 상태를 함께 확인(쿼리 왕복 증가 없음).</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>live_platform_tenant 11→13 (중지 전 토큰이 중지 후 403·재개 후 같은 토큰 복귀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="inlineStr">
+        <is>
+          <t>부하 중 UI 스위트 실패의 실제 원인 수정</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="inlineStr">
+        <is>
+          <t>to_menu() 가 패널 미렌더 시 조용히 조기 반환해, tree_click 이 없는 라벨을 기다리다 죽었다(실패 메시지가 원인을 가림). 1회 재시도 후 실패시키도록 변경 — UI 스위트 36종 공용.</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>live_f7_diff·live_f3_rbac_ui 재실행 통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>패널 바인딩 대상 등록 검증 (#17)</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>targetRef 가 비어 있지만 않으면 무엇이든 등록됐고, 셸은 모르는 값을 무시한 뒤 우측 패널을 전체 공개했다 — 오타 하나로 'Table 만' 이 '전부 보임' 이 되는데 화면에는 등록한 대로 표시된다. 운영 데이터의 RIGHT 바인딩 4건이 전부 미인식 키였다. Template 은 알려진 키·SCREEN 은 '/' 경로·PROCESS 는 '*' 또는 노드 id 로 제한.</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>live_head_registry 36→43 (미지 Template 422·경로 형식 422·정상 등록 201 대조군)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7028,6 +7028,28 @@
       <c r="D151" s="11" t="inlineStr">
         <is>
           <t>live_head_registry 36→43 (미지 Template 422·경로 형식 422·정상 등록 201 대조군)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>노드 이동의 접두 LIKE 리터럴화 (#24)</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="inlineStr">
+        <is>
+          <t>이동은 접두 LIKE 로 하위와 참조 자산을 연쇄 갱신하는데 base 를 리터럴화하지 않아, 노드명의 '_' 가 '아무 한 글자' 로 읽혔다. DB 로 의미 확인 — '/mv-a/aXb/kid' LIKE '/mv-a/a_b/%' 는 true. 형제 가지의 하위 주소까지 다시 쓰이고 moved 수치도 부풀어 이력으로도 드러나지 않았다. 이동·복제·영향분석 4개 지점 수정(9.32 가 영향분석에만 적용돼 있던 것).</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>live_u18_node_move 25→32 (밑줄 노드와 동일 자리 다른 글자 형제를 나란히 두고 이동 — 형제·자식 제자리 확인)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D152"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7050,6 +7050,50 @@
       <c r="D152" s="11" t="inlineStr">
         <is>
           <t>live_u18_node_move 25→32 (밑줄 노드와 동일 자리 다른 글자 형제를 나란히 두고 이동 — 형제·자식 제자리 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>고아 자산 탐지 정확화 + 탐지기 발화 검증 (#25)</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>hierarchy_validate 의 고아 자산 검사가 LIKE 접두 비교라 노드 주소의 '_' 가 와일드카드로 읽혀 진짜 고아를 놓쳤다(패턴이 컬럼이라 이스케이프 불가 — left() 비교로 전환). 또 상시 감시는 '이상 0건' 만 확인해 탐지기가 고장 나도 초록이었다.</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>live_structure_integrity 14→18 (고아 자산을 심어 ORPHAN_ASSET 탐지·ok=false 확인 후 제거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="B154" s="11" t="inlineStr">
+        <is>
+          <t>없어진 테넌트의 잔재 993행 정리 + 재발 방지</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="inlineStr">
+        <is>
+          <t>프로브 테넌트를 만드는 스위트 6종이 정리 목록을 각자 들고 있었고 2종에서 sys_hierarchy 가 빠져 매 실행 3행씩 남았다. 테넌트 행이 없어 화면에도 안 보이고 잔재 게이트는 전체 건수만 보아 드러나지 않았다. 정리 목록을 tests/_tenant.py 한 곳으로 모으고, 잔재 게이트에 '주인 없는 행'(tenant_id NOT IN sys_tenant) 지문을 추가했다.</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>live_ai_prep 27/27·live_security_anomaly 13/13 재실행 후 잔재 0 · 기존 993행(+감사 5행) 제거, 운영 테넌트 무영향</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7094,6 +7094,28 @@
       <c r="D154" s="11" t="inlineStr">
         <is>
           <t>live_ai_prep 27/27·live_security_anomaly 13/13 재실행 후 잔재 0 · 기존 993행(+감사 5행) 제거, 운영 테넌트 무영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="B155" s="11" t="inlineStr">
+        <is>
+          <t>승인 당시 전개 근거 지문 + basisDrift (#35)</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>승인된 관계는 삭제가 막히는데(DRAFT 한정) 슬롯 매핑은 자유롭게 바뀌었다 — 매핑은 BOM 전개의 유일한 근거이므로 승인 이후 바뀌면 승인된 내용과 현재 내용이 다른데 화면은 APPROVED 만 보여 줬다. 승인 시점 지문(approved_basis_hash, alembic 0064)을 남기고 현재 지문과 다르면 basisDrift 로 노출. 횟수가 아니라 내용 비교라 되돌리면 드리프트가 사라진다. 기존 승인 관계 14건은 backfill 로 오탐 방지.</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>live_slot_map 19→22 (드리프트 발생·복원 시 소멸·필드 노출) · DB 정의서 컬럼 1190→1191 갱신</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7116,6 +7116,28 @@
       <c r="D155" s="11" t="inlineStr">
         <is>
           <t>live_slot_map 19→22 (드리프트 발생·복원 시 소멸·필드 노출) · DB 정의서 컬럼 1190→1191 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="B156" s="11" t="inlineStr">
+        <is>
+          <t>동일 조합 동시 생성의 정직한 응답 (#28)</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="inlineStr">
+        <is>
+          <t>중복 검사(SELECT)와 INSERT 사이 창에서 부분 UNIQUE(ux_product_code_combo)에 걸리면 500 이 나갔다 — 혼자 눌렀을 때는 409 로 안내하는 같은 상황이다. 트랜잭션 격리상 동시 요청은 서로의 미커밋 행을 볼 수 없어 사전 검사로는 막을 수 없다. 제약 위반을 409 로 변환.</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>live_product_builder 34→37 (스레드 5 동시 생성 [409,409,409,201,409] · 코드 1벌 · 서버 로그 500/Traceback 0건)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7138,6 +7138,28 @@
       <c r="D156" s="11" t="inlineStr">
         <is>
           <t>live_product_builder 34→37 (스레드 5 동시 생성 [409,409,409,201,409] · 코드 1벌 · 서버 로그 500/Traceback 0건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="B157" s="11" t="inlineStr">
+        <is>
+          <t>Diff Review 미리보기 절단 명시 (#32)</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>dryRun 미리보기가 diff[:50] 으로 잘리면서 그 사실을 말하지 않았다 — 검토 화면은 반영 여부를 판단하는 자리라 일부를 전량으로 읽으면 곤란하다(17.10·18.83 과 같은 계열). diffTotal/diffTruncated/diffLimit 반환 + 화면에 '미리보기 50/N행' 표기.</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>live_triage 23→27 (60행 잘림 표기·총 건수 전량 보고·1행 대조군 미절단)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7160,6 +7160,28 @@
       <c r="D157" s="11" t="inlineStr">
         <is>
           <t>live_triage 23→27 (60행 잘림 표기·총 건수 전량 보고·1행 대조군 미절단)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t>19.10</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>Where-used 깊이 상한 절단 명시 (#34)</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr">
+        <is>
+          <t>역전개 재귀가 up.level &lt; maxLevel 로 조용히 끊겨, 상한을 넘는 체인이 '거기서 끝나는 구조' 로 보였다. 하향 전개는 같은 이유로 이미 depthCapped 를 알리고 있었는데 역전개만 빠져 있었다. depthCapped/depthLimit 반환 + 코드 상세 화면에 끊김 표기.</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>live_triage 27→29 (L1 요청 시 끊김 표기·L20 대조군 미절단)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7182,6 +7182,28 @@
       <c r="D158" s="11" t="inlineStr">
         <is>
           <t>live_triage 27→29 (L1 요청 시 끊김 표기·L20 대조군 미절단)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>19.11</t>
+        </is>
+      </c>
+      <c r="B159" s="11" t="inlineStr">
+        <is>
+          <t>Config Snapshot 표시 정정 (#39·#42)</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
+        <is>
+          <t>Handoff 목록·Output Package 가 configSnapshotId 라는 이름으로 선택안 id 를 돌려주고 화면은 'Config Snapshot #123' 으로 보여 줬다 — 번호 체계가 달라 그 번호로 스냅샷을 찾으면 없다. 실측 20건 중 실제 고정 0건인데 전건에 번호가 찍혀 있었다. selectionId 와 configSnapshotId(실제 sys_snapshot id, 미고정은 null)로 분리하고 화면은 '미고정'을 명시.</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>live_triage 29→33 (고정 시 번호 일치·선택안 id 와 상이·조회 가능 · 미고정 null) · API 계약 문서 갱신</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7204,6 +7204,28 @@
       <c r="D159" s="11" t="inlineStr">
         <is>
           <t>live_triage 29→33 (고정 시 번호 일치·선택안 id 와 상이·조회 가능 · 미고정 null) · API 계약 문서 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>19.13</t>
+        </is>
+      </c>
+      <c r="B160" s="11" t="inlineStr">
+        <is>
+          <t>테스트 Run 의 ERP 이관 차단 (#44·#45)</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr">
+        <is>
+          <t>가드 주석은 '임시 Run 차단' 이라 적혀 있었으나 is_test 를 읽지 않아, 테스트로 표시한 실행이 ERP 로 넘어가 작업지시·구매의 근거가 될 수 있었다(18.80 은 같은 값으로 납품물에서 제외한다). 검증도 그 상태를 정상으로 단언하고 있었다. 가드 추가 + 검증은 차단을 먼저 밟고 상태기계는 정식 Run 으로 진행 후 원복.</t>
+        </is>
+      </c>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>live_triage 33→34 (테스트 Run Handoff 422) · live_snapshot 13/13 · UI 실행 Run 정리(자기 생성분만 표기, 잔재 0)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7226,6 +7226,28 @@
       <c r="D160" s="11" t="inlineStr">
         <is>
           <t>live_triage 33→34 (테스트 Run Handoff 422) · live_snapshot 13/13 · UI 실행 Run 정리(자기 생성분만 표기, 잔재 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>19.14</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="inlineStr">
+        <is>
+          <t>UI 실행 Run 원복 공용화 + 잔재 탐지</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
+        <is>
+          <t>화면 Run 을 누르는 스위트가 만든 정식 Run 이 남으면 프로젝트의 최신 SUCCESS Run 이 되어 고객 전달 패키지 내용이 바뀐다(18.77·18.80). 한 스위트만 고쳤더니 다른 스위트에서 또 나와, 정리 로직을 tests/_runs.py 로 모으고(실행 전 max(run_id) 기준) 잔재 지문에 '비-테스트 Run 수' 를 추가해 다음부터는 함대가 즉시 실패하도록 했다.</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>live_f4_noop 18/18(2건 원복 실증) · live_b18_cost 22/22 · 기존 잔재 4건 정리, 기준선 32건</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7248,6 +7248,28 @@
       <c r="D161" s="11" t="inlineStr">
         <is>
           <t>live_f4_noop 18/18(2건 원복 실증) · live_b18_cost 22/22 · 기존 잔재 4건 정리, 기준선 32건</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>19.15</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>보관 정리 상한 고지 + 검증의 실 이력 삭제 정정 (E3)</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr">
+        <is>
+          <t>live_run_retention 이 '지우지 않는 경로 검증' 을 표방하며 상수 100 을 넘겨, Run 이 100건을 넘어선 뒤부터 함대마다 오래된 Run 13건을 영구 삭제하고 그것을 정상으로 단언했다. 서버도 keepLatest 를 상한 100 으로 조용히 낮추고 있었다. 상한은 유지하되 낮춘 사실을 응답에 명시(keepLatestRequested/Capped + 사유), 스위트는 상한 고지 검증으로 전환. 함대 생성 Run 잔재 검사는 러너로 이동(시작 시 max(run_id) 기준).</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>live_run_retention 16/16 · 러너에 '함대 생성 Run 정리 확인' 단계 신설</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7270,6 +7270,28 @@
       <c r="D162" s="11" t="inlineStr">
         <is>
           <t>live_run_retention 16/16 · 러너에 '함대 생성 Run 정리 확인' 단계 신설</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>19.16</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>Run 화면 진입 시 자동 실행 정정 (#43)</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr">
+        <is>
+          <t>RunPanel 이 화면 진입 즉시 파이프라인을 시작해, 메뉴로 열기만 해도 BOM·원가·산출물이 생성되고 그 Run 이 프로젝트의 최신 SUCCESS Run 이 되어 고객 전달 패키지 내용이 바뀌었다(18.77·18.80). 'Run ▶'(selectionId 동반) 진입만 자동 시작하고, 그 밖에는 최근 Run 표시 + 실행 버튼. 화면에 '열기만 해서는 실행하지 않습니다' 명시(EN/JA/ZH 시드).</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>live_demo_scenario 16/16 · Run 수 112→112 불변 · live_b18_cost 22/22(버튼 경로 정상)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7292,6 +7292,28 @@
       <c r="D163" s="11" t="inlineStr">
         <is>
           <t>live_demo_scenario 16/16 · Run 수 112→112 불변 · live_b18_cost 22/22(버튼 경로 정상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>19.17</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>링크 없는 Run 산출물의 삭제 차단 (#53·#55)</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>DELETE /files/{id} 가 참조 행(cpq_output·cst_quotation)이 있을 때만 막았다. Run 보관 정리는 cpq_output 을 지우고 파일은 남기므로(#53), 운영 데이터 OUTPUT 6,693건 중 6,369건이 링크 없는 상태로 삭제 가능했다. 편집 경로가 이미 쓰던 _assert_mutable 을 삭제 경로에도 적용.</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>live_file_role 25→28 (링크 없는 산출물 409·거부 후 잔존 확인·작도 원본은 삭제 가능 대조군)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -3700,7 +3700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7314,6 +7314,28 @@
       <c r="D164" s="11" t="inlineStr">
         <is>
           <t>live_file_role 25→28 (링크 없는 산출물 409·거부 후 잔존 확인·작도 원본은 삭제 가능 대조군)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>19.18</t>
+        </is>
+      </c>
+      <c r="B165" s="11" t="inlineStr">
+        <is>
+          <t>훼손된 활성 패키지의 고객 배포 차단 (#61·#69)</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr">
+        <is>
+          <t>GET /toolbox/runtime 은 활성 패키지 체크섬을 재계산해 intact:false 로 훼손을 알리지만, 고객사 배포 경로(POST /support/packages)는 그 신호를 읽지 않아 훼손·부분 수정 상태로도 배포됐다. 배포 시점에 게시 당시 체크섬과 대조해 409 로 차단.</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>live_support_access 24→28 (훼손 주입→런타임 경고→배포 409→원복 대조군)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_Launch준비상태.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,9 @@
     </font>
     <font>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -100,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -135,6 +138,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -632,12 +636,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>라이브 API 플릿 (139 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 13종</t>
+          <t>라이브 API 플릿 (139 스위트·실 HTTP+psql, 시드 자기치유 포함) + 정적/브라우저 게이트 13종 + 러너 잔재 검사 1종</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PASS 152/152 (스위트 139 + 게이트 13종 · 2026-07-28). 중간 배포 없음을 러너가 확인(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2·18.6)·산출물 결정성(18.10)·대화 절단(18.11)·목록 절단 고지(18.14)·삭제 이력 보존(18.16) 반영</t>
+          <t>PASS 153/153 (스위트 139 + 게이트 13종 + 러너 검사 1 · 2026-07-28). 중간 배포 없음을 러너가 확인(/health.proc 불변). 승인 상태 기계(17.1~17.9)·인쇄리포트/Import(17.10~17.12)·문서 생성 전환(18.2·18.6)·산출물 결정성(18.10)·대화 절단(18.11)·목록 절단 고지(18.14)·삭제 이력 보존(18.16) 반영</t>
         </is>
       </c>
     </row>
@@ -713,7 +717,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>P0/P1 요구사항 63/63 구현·검증 완료. 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 7건(게이트로 증가 차단, 위험 순 축소 중).</t>
+          <t>P0/P1 요구사항 63/63 구현·검증 완료. 2026-07-28 **P0 전 줄 재감사 완료** — 요구 47줄(Foundation 10·Main Shell 6·Head/Hierarchy 5·PLM RCCS 10·CPQ 8·ERP Handoff 6·Drawing 2)을 구현 정독 + 조건별 실행으로 재확인해 **결함 22건** 조치. 불변식을 가진 P1(#57·#61·#62·#63·#69)도 같은 방식으로 확인해 1건 조치(19.18). 동시성·자원고갈 하드닝(9.16~9.22)·마스터/트랜잭션 검색(9.23~9.31)·정보접근 마스킹 우회 차단(9.37)·i18n 62화면 파리티(3로케일)·접근성 4개 WCAG 축(9.38~9.41). 2026-07-26 구간에서 인증 하드닝 3건(세션 서명키 기본값·비밀번호 해시·복구 경로)과 운영 데이터 실결함 4건(단가 미해결이 견적을 낮추던 경로·업무 날짜 하루 밀림·계층 이동 손상·토큰 서명키)을 실측 근거와 함께 해소했고, 규격 미구현 3건(CPQ-001 제품 선택·DOC-001 문서 개정·ADM-003 승인 위임)을 구현했다. 전 화면 62/62 · 플릿 131/131(스위트 121 + 게이트 10종) 실측. 구현 스코프 launch 가능. 잔여는 사용자 결정(#72~#80)·AI 크레딧 대기·감사 커버리지 7건(게이트로 증가 차단, 위험 순 축소 중).</t>
         </is>
       </c>
     </row>
@@ -728,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -737,6 +741,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -770,6 +775,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>재감사 (2026-07-28)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -798,6 +808,11 @@
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.1 중지 고객사의 기존 세션이 최대 8시간 유효)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -826,6 +841,11 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.0 OTP 연속 실패가 계정 잠금에 미포함)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -854,6 +874,11 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(18.99 EXECUTE 동사 미실효) + 정적 게이트 결함 2건 동시 수정</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -886,6 +911,11 @@
           <t>조회 가능 ≠ Export 가능</t>
         </is>
       </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(18.98 폴더 일괄 ZIP 반출 통제 부재, 견적서 83건 1.9MB 실증)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -914,6 +944,11 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 권한 상승 없음 확인 · 계약 불일치 1건 조치(18.96)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -942,6 +977,11 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고 · 시간 만료 검증 신설(18.95)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -970,6 +1010,11 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(18.94 PCR 감사 누락, 132건 전량 MASKED_READ)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -998,6 +1043,11 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고 · 동시 결정 경합 검증 신설(18.97)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1030,6 +1080,11 @@
           <t>핵심 불변식</t>
         </is>
       </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(체크섬 재계산·drift 대조)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1058,6 +1113,11 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고 · 검증 신설(18.93) → 잠금 결함은 #2 로 조치</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1178,6 +1238,11 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(레벨 기반 필터·System Head 가드)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1266,6 +1331,11 @@
           <t>구조의 심장</t>
         </is>
       </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.3 바인딩 대상 미검증, 오타 시 우측 패널 전체 공개)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1294,6 +1364,11 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(표시 설정과 구조 분리·게시본도 표시 변경 가능)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1322,6 +1397,11 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(center 바인딩 게이트·게시본 잠금)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1382,6 +1462,11 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(항상 DRAFT 생성·상태기계)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1410,6 +1495,11 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(잠금 노드 가드·형제 동명 409)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1438,6 +1528,11 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(표준 노드 보호·복제 시 승인/잠금/시스템표시 미승계)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1466,6 +1561,11 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.4 접두 LIKE 미이스케이프로 형제 가지 주소 오염)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1494,6 +1594,11 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.5 고아 자산 탐지 누락 + 탐지기 발화 미검증)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1582,6 +1687,11 @@
           <t>핵심 불변식 — 자유텍스트 등록은 Slot 미정의 그룹(GEN)만</t>
         </is>
       </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.8 동시 조합 생성 시 500)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1694,6 +1804,11 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.9 Diff 미리보기 50행 무음 절단)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1750,6 +1865,11 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.10 역전개 깊이 상한 무음 절단)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1778,6 +1898,11 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.7 승인 후 전개 근거 변경이 은폐됨)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1890,6 +2015,11 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.11 configSnapshotId 가 선택안 id 반환)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1922,6 +2052,11 @@
           <t>결과는 Snapshot(#9)이, 근거는 rel_basis 가 보존</t>
         </is>
       </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(rel_basis 고정·체크섬 대조·옛 Run 은 null 로 정직)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1950,6 +2085,11 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(Run 완료 시 결과 동결)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1978,6 +2118,11 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.11 동일)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2006,6 +2151,11 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.16 화면 진입만으로 파이프라인 자동 실행)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2034,6 +2184,11 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(SUCCESS·BOM 필수, 원가/견적서 warning)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2062,6 +2217,11 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.13 테스트 Run 의 ERP 이관 차단 누락)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2094,6 +2254,11 @@
           <t>ERP 는 승인 Package 만 수신</t>
         </is>
       </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(미승인 수신 409)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2122,6 +2287,11 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(재생성 시 supersede)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2298,6 +2468,11 @@
           <t>핵심 불변식 — 산출물 편집/덮어쓰기 409, 동명 저장은 별도 SOURCE 행</t>
         </is>
       </c>
+      <c r="G54" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.17 링크 없는 산출물 6,369건 삭제 가능)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2354,6 +2529,11 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.17 동일)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2410,6 +2590,11 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(원본 읽기전용·부분 Lock·삭제 보호)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2522,6 +2707,11 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 결함 1건 조치(19.18 훼손 패키지의 고객 배포 차단)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -2550,6 +2740,11 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(패키지 스냅샷만 평가·엔진에 쓰기 경로 없음)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2578,6 +2773,11 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(게시 이력 버전만·DEPLOY 동사·런타임이 포인터를 실제로 읽음)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -2754,6 +2954,11 @@
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t>재감사 — 견고(이중 승인 순서 강제·대상 테넌트만)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
